--- a/收集的公开数据/忘川风华录_视频数据完全版.xlsx
+++ b/收集的公开数据/忘川风华录_视频数据完全版.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="6880"/>
+    <workbookView windowWidth="21600" windowHeight="9555" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="忘川风华录_视频数据_提取完成" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3060" uniqueCount="939">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3077" uniqueCount="943">
   <si>
     <t>序号</t>
   </si>
@@ -3786,6 +3786,59 @@
 只怕无佳期永慕相望
 我待曙色沾霜　才知南柯一场
 留下这传奇　在水一方流浪</t>
+  </si>
+  <si>
+    <t>78.6万</t>
+  </si>
+  <si>
+    <t>1.2万</t>
+  </si>
+  <si>
+    <t>忘川风华录手游五周年主题曲《大风起兮》今日上线！ 出品：《忘川风华录》手游 演唱：星尘infinity、海伊、苍穹、诗岸、永夜Minus、赤羽、牧心 调校：坐标P 词：赵素冰 十灯 | 曲：刘兆伦 @灼梦Studio 莲琊 编曲：丁嘉昱@灼梦Studio/蔡成钰@灼梦Studio 笛箫：丁晓逵 | 吉他/贝斯：吴余涛 | 古筝：莲琊 弦乐：国际首席爱乐乐团 | 弦乐录音棚：金田录音棚 弦乐录音师：王小四 | 弦乐监制：李朋 和声监制：莲琊 | 和声编写：周弦 和声：周弦/唐子超 | 混音/母带：王昆 制作统筹：欧阳文俊 | 制作人：莲琊 音乐制作团队：潮声组 视频：麻薯映像 协力：忘川风华录 祖传艺能：htt下ps://pan.baidu.co周m/s/1pVl7Q-Pc放SMQupwHNC1VCW入Q?pwd=drmk 【drmk】</t>
+  </si>
+  <si>
+    <t>上告肃穆兮　承予宗
+下思厥功兮　兴汉风
+国士无双兵戈韬略无穷
+博浪沙前地惊天动
+观麟相凤　谁大德清雍
+奔骏龙城临疆当风
+狼山功冠无与相同
+千古去惟天与公
+大风　歌飒飒兮　立天地　兴汉家
+可见荠麦黍华　丰集于下
+陵阙　武治四貊　功在甲子　威仪广大
+帝王骨　载万槎
+凤鸣　声震震兮　夜栖枝　旦辞霞
+自与龙矫虎飒　竞分天下
+月照　未央宫中　故纸册上　一笔朱砂
+名垂　万家
+驼月挂风霜　身毅心雄
+戎地夷路远漠中
+史篇毫墨挥动万世其中
+纸载笔绘庙柏何荣
+千秋汉书谁颖慧明通
+雁辞汉宫　离群击空
+穆穆解忧　怆怆北风
+朱颜　更似　红日红
+鸟雀　飞杳杳兮　水田雨润　桑麻
+仁怀　垂治四海　未老芳华
+春秋　几覆陇亩　繁华不过　寻常人家
+千古共成佳话
+琴剑　鸣铮铮兮　少年鹰扬　纵马
+一箭　江火燃夜　筹谋风雅
+鹤扇　指点岁华　流星飒踏　披照银甲
+铜雀　生花
+我与山河共休矣
+春来汝便当归
+开疆　王侯将相　多少风流生涯
+英雄豪杰　几度　岁月年华
+身前　千里烟沙　生后万姓　呼我汉家
+千秋业　青史答　
+山河　雄关之外　万立青天之下
+壮心　几许豪壮　几许飒沓
+汉魂　何曾淡寡　鼎立苍穹　赓续万家
+不负　后世　华夏</t>
   </si>
   <si>
     <t xml:space="preserve">我有一则今古无人做的梦　今日要这天下和我与共
@@ -5385,14 +5438,14 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1"/>
   </cellXfs>
@@ -5929,16 +5982,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AA55"/>
-  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9.8141592920354" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9.81818181818182" style="1"/>
-    <col min="2" max="3" width="22.2727272727273" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.81818181818182" style="1"/>
-    <col min="5" max="5" width="11.8181818181818" style="2"/>
-    <col min="6" max="24" width="9.81818181818182" style="1"/>
-    <col min="25" max="25" width="27.9090909090909" style="1" customWidth="1"/>
-    <col min="26" max="26" width="16.8181818181818" style="1" customWidth="1"/>
-    <col min="27" max="16384" width="9.81818181818182" style="1"/>
+    <col min="1" max="1" width="9.8141592920354" style="1"/>
+    <col min="2" max="3" width="22.2743362831858" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.8141592920354" style="1"/>
+    <col min="5" max="5" width="11.8141592920354" style="2"/>
+    <col min="6" max="24" width="9.8141592920354" style="1"/>
+    <col min="25" max="25" width="27.9115044247788" style="1" customWidth="1"/>
+    <col min="26" max="26" width="16.8141592920354" style="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.8141592920354" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27">
@@ -5954,7 +6007,7 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
@@ -10516,17 +10569,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:AA45"/>
-  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14"/>
+  <dimension ref="A1:AH46"/>
+  <sheetFormatPr defaultColWidth="9.8141592920354" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9.81818181818182" style="1"/>
-    <col min="2" max="3" width="22.2727272727273" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.81818181818182" style="1"/>
-    <col min="5" max="5" width="11.8181818181818" style="2"/>
-    <col min="6" max="16384" width="9.81818181818182" style="1"/>
+    <col min="1" max="1" width="9.8141592920354" style="1"/>
+    <col min="2" max="3" width="22.2743362831858" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.8141592920354" style="1"/>
+    <col min="5" max="5" width="11.8141592920354" style="2"/>
+    <col min="6" max="16384" width="9.8141592920354" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:27">
+    <row r="1" s="1" customFormat="1" spans="1:34">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -10539,7 +10592,7 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="11" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="4" t="s">
@@ -10609,309 +10662,305 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:27">
+    <row r="2" s="1" customFormat="1" spans="1:34">
       <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="6">
+        <v>46101</v>
+      </c>
+      <c r="F2" s="6" t="s">
+        <v>657</v>
+      </c>
+      <c r="G2" s="6">
+        <v>786000</v>
+      </c>
+      <c r="H2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>658</v>
+      </c>
+      <c r="J2" s="6">
+        <v>12000</v>
+      </c>
+      <c r="K2" s="6" t="s">
+        <v>360</v>
+      </c>
+      <c r="L2" s="6">
+        <v>40000</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>495</v>
+      </c>
+      <c r="N2" s="6">
+        <v>31000</v>
+      </c>
+      <c r="O2" s="6" t="s">
+        <v>130</v>
+      </c>
+      <c r="P2" s="6">
+        <v>25000</v>
+      </c>
+      <c r="Q2" s="6" t="s">
+        <v>659</v>
+      </c>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6" t="s">
+        <v>660</v>
+      </c>
+      <c r="V2" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="W2" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="X2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA2" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG2" s="12"/>
+      <c r="AH2" s="12"/>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:34">
+      <c r="A3" s="6">
         <v>2</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B3" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C3" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D3" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E2" s="13">
+      <c r="E3" s="13">
         <v>46063.75</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="G2" s="6">
+      <c r="G3" s="6">
         <v>2390000</v>
-      </c>
-      <c r="H2" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J2" s="6">
-        <v>24000</v>
-      </c>
-      <c r="K2" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="L2" s="6">
-        <v>125000</v>
-      </c>
-      <c r="M2" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="N2" s="6">
-        <v>101000</v>
-      </c>
-      <c r="O2" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="P2" s="6">
-        <v>71000</v>
-      </c>
-      <c r="Q2" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="R2" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="S2" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="T2" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="U2" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="V2" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="W2" s="6" t="s">
-        <v>60</v>
-      </c>
-      <c r="X2" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="Y2" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="Z2" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="AA2" s="6" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="3" s="1" customFormat="1" spans="1:27">
-      <c r="A3" s="6">
-        <v>3</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>66</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>67</v>
-      </c>
-      <c r="E3" s="13">
-        <v>45947.75</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>68</v>
-      </c>
-      <c r="G3" s="6">
-        <v>1027000</v>
       </c>
       <c r="H3" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="I3" s="6">
-        <v>6070</v>
+      <c r="I3" s="6" t="s">
+        <v>50</v>
       </c>
       <c r="J3" s="6">
-        <v>6070</v>
+        <v>24000</v>
       </c>
       <c r="K3" s="6" t="s">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="L3" s="6">
-        <v>50000</v>
+        <v>125000</v>
       </c>
       <c r="M3" s="6" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="N3" s="6">
-        <v>37000</v>
+        <v>101000</v>
       </c>
       <c r="O3" s="6" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="P3" s="6">
-        <v>30000</v>
+        <v>71000</v>
       </c>
       <c r="Q3" s="6" t="s">
-        <v>72</v>
+        <v>54</v>
       </c>
       <c r="R3" s="6" t="s">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="S3" s="6" t="s">
-        <v>74</v>
+        <v>56</v>
       </c>
       <c r="T3" s="6" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="U3" s="6" t="s">
-        <v>76</v>
+        <v>58</v>
       </c>
       <c r="V3" s="6" t="s">
-        <v>77</v>
+        <v>59</v>
       </c>
       <c r="W3" s="6" t="s">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="X3" s="6" t="s">
-        <v>79</v>
+        <v>61</v>
       </c>
       <c r="Y3" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="Z3" s="6" t="s">
-        <v>80</v>
+        <v>63</v>
       </c>
       <c r="AA3" s="6" t="s">
-        <v>79</v>
+        <v>64</v>
       </c>
     </row>
-    <row r="4" s="1" customFormat="1" spans="1:27">
+    <row r="4" s="1" customFormat="1" spans="1:34">
       <c r="A4" s="6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>81</v>
+        <v>65</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>82</v>
+        <v>66</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>83</v>
+        <v>67</v>
       </c>
       <c r="E4" s="13">
-        <v>45803.75</v>
+        <v>45947.75</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="G4" s="6">
-        <v>2567000</v>
+        <v>1027000</v>
       </c>
       <c r="H4" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="I4" s="6" t="s">
-        <v>85</v>
+      <c r="I4" s="6">
+        <v>6070</v>
       </c>
       <c r="J4" s="6">
-        <v>29000</v>
+        <v>6070</v>
       </c>
       <c r="K4" s="6" t="s">
-        <v>86</v>
+        <v>69</v>
       </c>
       <c r="L4" s="6">
-        <v>132000</v>
+        <v>50000</v>
       </c>
       <c r="M4" s="6" t="s">
-        <v>87</v>
+        <v>70</v>
       </c>
       <c r="N4" s="6">
-        <v>82000</v>
+        <v>37000</v>
       </c>
       <c r="O4" s="6" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="P4" s="6">
-        <v>75000</v>
+        <v>30000</v>
       </c>
       <c r="Q4" s="6" t="s">
-        <v>89</v>
+        <v>72</v>
       </c>
       <c r="R4" s="6" t="s">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="S4" s="6" t="s">
-        <v>37</v>
+        <v>74</v>
       </c>
       <c r="T4" s="6" t="s">
-        <v>37</v>
+        <v>75</v>
       </c>
       <c r="U4" s="6" t="s">
-        <v>91</v>
+        <v>76</v>
       </c>
       <c r="V4" s="6" t="s">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="W4" s="6" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="X4" s="6" t="s">
-        <v>93</v>
+        <v>79</v>
       </c>
       <c r="Y4" s="6" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="Z4" s="6" t="s">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AA4" s="6" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
     </row>
-    <row r="5" s="1" customFormat="1" spans="1:27">
+    <row r="5" s="1" customFormat="1" spans="1:34">
       <c r="A5" s="6">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>111</v>
+        <v>81</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>112</v>
+        <v>82</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>113</v>
+        <v>83</v>
       </c>
       <c r="E5" s="13">
-        <v>45679.5</v>
+        <v>45803.75</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="G5" s="6">
-        <v>2258000</v>
+        <v>2567000</v>
       </c>
       <c r="H5" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>115</v>
+        <v>85</v>
       </c>
       <c r="J5" s="6">
-        <v>11000</v>
+        <v>29000</v>
       </c>
       <c r="K5" s="6" t="s">
-        <v>116</v>
+        <v>86</v>
       </c>
       <c r="L5" s="6">
-        <v>93000</v>
+        <v>132000</v>
       </c>
       <c r="M5" s="6" t="s">
-        <v>117</v>
+        <v>87</v>
       </c>
       <c r="N5" s="6">
-        <v>74000</v>
+        <v>82000</v>
       </c>
       <c r="O5" s="6" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="P5" s="6">
-        <v>60000</v>
+        <v>75000</v>
       </c>
       <c r="Q5" s="6" t="s">
-        <v>119</v>
+        <v>89</v>
       </c>
       <c r="R5" s="6" t="s">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="S5" s="6" t="s">
         <v>37</v>
@@ -10920,425 +10969,425 @@
         <v>37</v>
       </c>
       <c r="U5" s="6" t="s">
-        <v>121</v>
+        <v>91</v>
       </c>
       <c r="V5" s="6" t="s">
-        <v>122</v>
+        <v>92</v>
       </c>
       <c r="W5" s="6" t="s">
-        <v>123</v>
+        <v>60</v>
       </c>
       <c r="X5" s="6" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="Y5" s="6" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="Z5" s="6" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
       <c r="AA5" s="6" t="s">
-        <v>60</v>
+        <v>96</v>
       </c>
     </row>
-    <row r="6" s="1" customFormat="1" spans="1:27">
+    <row r="6" s="1" customFormat="1" spans="1:34">
       <c r="A6" s="6">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>125</v>
+        <v>111</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>126</v>
+        <v>112</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>127</v>
+        <v>113</v>
       </c>
       <c r="E6" s="13">
-        <v>45590.75</v>
+        <v>45679.5</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="G6" s="6">
-        <v>1008000</v>
+        <v>2258000</v>
       </c>
       <c r="H6" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="I6" s="6">
-        <v>1406</v>
+      <c r="I6" s="6" t="s">
+        <v>115</v>
       </c>
       <c r="J6" s="6">
-        <v>1406</v>
+        <v>11000</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="L6" s="6">
-        <v>44000</v>
+        <v>93000</v>
       </c>
       <c r="M6" s="6" t="s">
-        <v>32</v>
+        <v>117</v>
       </c>
       <c r="N6" s="6">
-        <v>33000</v>
+        <v>74000</v>
       </c>
       <c r="O6" s="6" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="P6" s="6">
-        <v>25000</v>
+        <v>60000</v>
       </c>
       <c r="Q6" s="6" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="R6" s="6" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="S6" s="6" t="s">
         <v>37</v>
       </c>
       <c r="T6" s="6" t="s">
-        <v>133</v>
+        <v>37</v>
       </c>
       <c r="U6" s="6" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="V6" s="6" t="s">
-        <v>135</v>
+        <v>122</v>
       </c>
       <c r="W6" s="6" t="s">
-        <v>136</v>
+        <v>123</v>
       </c>
       <c r="X6" s="6" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="Y6" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="Z6" s="6" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="AA6" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="7" s="1" customFormat="1" spans="1:27">
+    <row r="7" s="1" customFormat="1" spans="1:34">
       <c r="A7" s="6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>139</v>
+        <v>125</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>140</v>
+        <v>126</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>141</v>
+        <v>127</v>
       </c>
       <c r="E7" s="13">
-        <v>45520.7500115741</v>
+        <v>45590.75</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="G7" s="6">
-        <v>2687000</v>
+        <v>1008000</v>
       </c>
       <c r="H7" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I7" s="6">
-        <v>3106</v>
+        <v>1406</v>
       </c>
       <c r="J7" s="6">
-        <v>3106</v>
+        <v>1406</v>
       </c>
       <c r="K7" s="6" t="s">
-        <v>143</v>
+        <v>129</v>
       </c>
       <c r="L7" s="6">
-        <v>84000</v>
+        <v>44000</v>
       </c>
       <c r="M7" s="6" t="s">
-        <v>144</v>
+        <v>32</v>
       </c>
       <c r="N7" s="6">
-        <v>69000</v>
+        <v>33000</v>
       </c>
       <c r="O7" s="6" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="P7" s="6">
-        <v>64000</v>
+        <v>25000</v>
       </c>
       <c r="Q7" s="6" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="R7" s="6" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="S7" s="6" t="s">
         <v>37</v>
       </c>
       <c r="T7" s="6" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="U7" s="6" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="V7" s="6" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="W7" s="6" t="s">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="X7" s="6" t="s">
-        <v>151</v>
+        <v>137</v>
       </c>
       <c r="Y7" s="6" t="s">
         <v>42</v>
       </c>
       <c r="Z7" s="6" t="s">
-        <v>63</v>
+        <v>138</v>
       </c>
       <c r="AA7" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" spans="1:27">
+    <row r="8" s="1" customFormat="1" spans="1:34">
       <c r="A8" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>152</v>
+        <v>139</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="E8" s="13">
-        <v>45450.75</v>
+        <v>45520.7500115741</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="G8" s="6">
-        <v>3583000</v>
+        <v>2687000</v>
       </c>
       <c r="H8" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I8" s="6">
-        <v>6465</v>
+        <v>3106</v>
       </c>
       <c r="J8" s="6">
-        <v>6465</v>
+        <v>3106</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="L8" s="6">
-        <v>97000</v>
+        <v>84000</v>
       </c>
       <c r="M8" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="N8" s="6">
+        <v>69000</v>
+      </c>
+      <c r="O8" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="N8" s="6">
+      <c r="P8" s="6">
         <v>64000</v>
       </c>
-      <c r="O8" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="P8" s="6">
-        <v>60000</v>
-      </c>
       <c r="Q8" s="6" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="R8" s="6" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="S8" s="6" t="s">
-        <v>159</v>
+        <v>37</v>
       </c>
       <c r="T8" s="6" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="U8" s="6" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
       <c r="V8" s="6" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
       <c r="W8" s="6" t="s">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="X8" s="6" t="s">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="Y8" s="6" t="s">
-        <v>94</v>
+        <v>42</v>
       </c>
       <c r="Z8" s="6" t="s">
-        <v>163</v>
+        <v>63</v>
       </c>
       <c r="AA8" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" spans="1:27">
+    <row r="9" s="1" customFormat="1" spans="1:34">
       <c r="A9" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="E9" s="13">
-        <v>45412.75</v>
+        <v>45450.75</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="G9" s="6">
-        <v>1616000</v>
+        <v>3583000</v>
       </c>
       <c r="H9" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I9" s="6">
-        <v>1338</v>
+        <v>6465</v>
       </c>
       <c r="J9" s="6">
-        <v>1338</v>
+        <v>6465</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="L9" s="6">
-        <v>62000</v>
+        <v>97000</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>104</v>
+        <v>145</v>
       </c>
       <c r="N9" s="6">
-        <v>46000</v>
+        <v>64000</v>
       </c>
       <c r="O9" s="6" t="s">
-        <v>169</v>
+        <v>118</v>
       </c>
       <c r="P9" s="6">
-        <v>42000</v>
+        <v>60000</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>170</v>
+        <v>157</v>
       </c>
       <c r="R9" s="6" t="s">
-        <v>171</v>
+        <v>158</v>
       </c>
       <c r="S9" s="6" t="s">
-        <v>172</v>
+        <v>159</v>
       </c>
       <c r="T9" s="6" t="s">
-        <v>173</v>
+        <v>160</v>
       </c>
       <c r="U9" s="6" t="s">
-        <v>174</v>
+        <v>161</v>
       </c>
       <c r="V9" s="6" t="s">
-        <v>92</v>
+        <v>162</v>
       </c>
       <c r="W9" s="6" t="s">
-        <v>175</v>
+        <v>60</v>
       </c>
       <c r="X9" s="6" t="s">
-        <v>176</v>
+        <v>79</v>
       </c>
       <c r="Y9" s="6" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="Z9" s="6" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="AA9" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" spans="1:27">
+    <row r="10" s="1" customFormat="1" spans="1:34">
       <c r="A10" s="6">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="E10" s="13">
-        <v>45328.75</v>
+        <v>45412.75</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="G10" s="6">
-        <v>2972000</v>
+        <v>1616000</v>
       </c>
       <c r="H10" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I10" s="6">
-        <v>5765</v>
+        <v>1338</v>
       </c>
       <c r="J10" s="6">
-        <v>5765</v>
+        <v>1338</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
       <c r="L10" s="6">
-        <v>92000</v>
+        <v>62000</v>
       </c>
       <c r="M10" s="6" t="s">
-        <v>195</v>
+        <v>104</v>
       </c>
       <c r="N10" s="6">
-        <v>59000</v>
+        <v>46000</v>
       </c>
       <c r="O10" s="6" t="s">
-        <v>196</v>
+        <v>169</v>
       </c>
       <c r="P10" s="6">
-        <v>58000</v>
+        <v>42000</v>
       </c>
       <c r="Q10" s="6" t="s">
-        <v>197</v>
+        <v>170</v>
       </c>
       <c r="R10" s="6" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="S10" s="6" t="s">
-        <v>37</v>
+        <v>172</v>
       </c>
       <c r="T10" s="6" t="s">
-        <v>199</v>
+        <v>173</v>
       </c>
       <c r="U10" s="6" t="s">
-        <v>200</v>
+        <v>174</v>
       </c>
       <c r="V10" s="6" t="s">
-        <v>201</v>
+        <v>92</v>
       </c>
       <c r="W10" s="6" t="s">
         <v>175</v>
@@ -11347,235 +11396,235 @@
         <v>176</v>
       </c>
       <c r="Y10" s="6" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="Z10" s="6" t="s">
-        <v>202</v>
+        <v>177</v>
       </c>
       <c r="AA10" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" spans="1:27">
+    <row r="11" s="1" customFormat="1" spans="1:34">
       <c r="A11" s="6">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>203</v>
+        <v>190</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>204</v>
+        <v>191</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>205</v>
+        <v>192</v>
       </c>
       <c r="E11" s="13">
-        <v>45254.75</v>
+        <v>45328.75</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>206</v>
+        <v>193</v>
       </c>
       <c r="G11" s="6">
-        <v>5002000</v>
+        <v>2972000</v>
       </c>
       <c r="H11" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>143</v>
+        <v>49</v>
+      </c>
+      <c r="I11" s="6">
+        <v>5765</v>
       </c>
       <c r="J11" s="6">
-        <v>84000</v>
+        <v>5765</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>208</v>
+        <v>194</v>
       </c>
       <c r="L11" s="6">
-        <v>120000</v>
+        <v>92000</v>
       </c>
       <c r="M11" s="6" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="N11" s="6">
-        <v>113000</v>
+        <v>59000</v>
       </c>
       <c r="O11" s="6" t="s">
-        <v>52</v>
+        <v>196</v>
       </c>
       <c r="P11" s="6">
-        <v>101000</v>
+        <v>58000</v>
       </c>
       <c r="Q11" s="6" t="s">
-        <v>210</v>
+        <v>197</v>
       </c>
       <c r="R11" s="6" t="s">
-        <v>211</v>
+        <v>198</v>
       </c>
       <c r="S11" s="6" t="s">
         <v>37</v>
       </c>
       <c r="T11" s="6" t="s">
-        <v>212</v>
+        <v>199</v>
       </c>
       <c r="U11" s="6" t="s">
-        <v>213</v>
+        <v>200</v>
       </c>
       <c r="V11" s="6" t="s">
-        <v>108</v>
+        <v>201</v>
       </c>
       <c r="W11" s="6" t="s">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="X11" s="6" t="s">
-        <v>79</v>
+        <v>176</v>
       </c>
       <c r="Y11" s="6" t="s">
-        <v>214</v>
+        <v>94</v>
       </c>
       <c r="Z11" s="6" t="s">
-        <v>215</v>
+        <v>202</v>
       </c>
       <c r="AA11" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" spans="1:27">
+    <row r="12" s="1" customFormat="1" spans="1:34">
       <c r="A12" s="6">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="E12" s="13">
-        <v>45221.5</v>
+        <v>45254.75</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="G12" s="6">
-        <v>4550000</v>
+        <v>5002000</v>
       </c>
       <c r="H12" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I12" s="6">
-        <v>9573</v>
+        <v>207</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>143</v>
       </c>
       <c r="J12" s="6">
-        <v>9573</v>
+        <v>84000</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
       <c r="L12" s="6">
-        <v>148000</v>
+        <v>120000</v>
       </c>
       <c r="M12" s="6" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
       <c r="N12" s="6">
-        <v>108000</v>
+        <v>113000</v>
       </c>
       <c r="O12" s="6" t="s">
-        <v>222</v>
+        <v>52</v>
       </c>
       <c r="P12" s="6">
-        <v>105000</v>
+        <v>101000</v>
       </c>
       <c r="Q12" s="6" t="s">
-        <v>223</v>
+        <v>210</v>
       </c>
       <c r="R12" s="6" t="s">
-        <v>224</v>
+        <v>211</v>
       </c>
       <c r="S12" s="6" t="s">
         <v>37</v>
       </c>
       <c r="T12" s="6" t="s">
-        <v>37</v>
+        <v>212</v>
       </c>
       <c r="U12" s="6" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="V12" s="6" t="s">
-        <v>150</v>
+        <v>108</v>
       </c>
       <c r="W12" s="6" t="s">
-        <v>60</v>
+        <v>136</v>
       </c>
       <c r="X12" s="6" t="s">
-        <v>109</v>
+        <v>79</v>
       </c>
       <c r="Y12" s="6" t="s">
-        <v>94</v>
+        <v>214</v>
       </c>
       <c r="Z12" s="6" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="AA12" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" spans="1:27">
+    <row r="13" s="1" customFormat="1" spans="1:34">
       <c r="A13" s="6">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="E13" s="13">
-        <v>45115.7500578704</v>
+        <v>45221.5</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="G13" s="6">
-        <v>1441000</v>
+        <v>4550000</v>
       </c>
       <c r="H13" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I13" s="6">
-        <v>1542</v>
+        <v>9573</v>
       </c>
       <c r="J13" s="6">
-        <v>1542</v>
+        <v>9573</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="L13" s="6">
-        <v>52000</v>
+        <v>148000</v>
       </c>
       <c r="M13" s="6" t="s">
-        <v>71</v>
+        <v>221</v>
       </c>
       <c r="N13" s="6">
-        <v>30000</v>
+        <v>108000</v>
       </c>
       <c r="O13" s="6" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="P13" s="6">
-        <v>28000</v>
+        <v>105000</v>
       </c>
       <c r="Q13" s="6" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
       <c r="R13" s="6" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
       <c r="S13" s="6" t="s">
         <v>37</v>
@@ -11584,271 +11633,271 @@
         <v>37</v>
       </c>
       <c r="U13" s="6" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="V13" s="6" t="s">
-        <v>236</v>
+        <v>150</v>
       </c>
       <c r="W13" s="6" t="s">
-        <v>237</v>
+        <v>60</v>
       </c>
       <c r="X13" s="6" t="s">
-        <v>238</v>
+        <v>109</v>
       </c>
       <c r="Y13" s="6" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="Z13" s="6" t="s">
-        <v>239</v>
+        <v>226</v>
       </c>
       <c r="AA13" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" spans="1:27">
+    <row r="14" s="1" customFormat="1" spans="1:34">
       <c r="A14" s="6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>240</v>
+        <v>227</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>241</v>
+        <v>228</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>242</v>
+        <v>229</v>
       </c>
       <c r="E14" s="13">
-        <v>45086.7500578704</v>
+        <v>45115.7500578704</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>243</v>
+        <v>230</v>
       </c>
       <c r="G14" s="6">
-        <v>2611000</v>
+        <v>1441000</v>
       </c>
       <c r="H14" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I14" s="6">
-        <v>2105</v>
+        <v>1542</v>
       </c>
       <c r="J14" s="6">
-        <v>2105</v>
+        <v>1542</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>244</v>
+        <v>231</v>
       </c>
       <c r="L14" s="6">
-        <v>76000</v>
+        <v>52000</v>
       </c>
       <c r="M14" s="6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N14" s="6">
-        <v>50000</v>
+        <v>30000</v>
       </c>
       <c r="O14" s="6" t="s">
-        <v>69</v>
+        <v>232</v>
       </c>
       <c r="P14" s="6">
-        <v>50000</v>
+        <v>28000</v>
       </c>
       <c r="Q14" s="6" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="R14" s="6" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="S14" s="6" t="s">
         <v>37</v>
       </c>
       <c r="T14" s="6" t="s">
-        <v>247</v>
+        <v>37</v>
       </c>
       <c r="U14" s="6" t="s">
-        <v>248</v>
+        <v>235</v>
       </c>
       <c r="V14" s="6" t="s">
-        <v>249</v>
+        <v>236</v>
       </c>
       <c r="W14" s="6" t="s">
-        <v>250</v>
+        <v>237</v>
       </c>
       <c r="X14" s="6" t="s">
-        <v>93</v>
+        <v>238</v>
       </c>
       <c r="Y14" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="Z14" s="6" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="AA14" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" spans="1:27">
+    <row r="15" s="1" customFormat="1" spans="1:34">
       <c r="A15" s="6">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>262</v>
+        <v>240</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>263</v>
+        <v>241</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>264</v>
+        <v>242</v>
       </c>
       <c r="E15" s="13">
-        <v>44988.75</v>
+        <v>45086.7500578704</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>265</v>
+        <v>243</v>
       </c>
       <c r="G15" s="6">
-        <v>3650000</v>
+        <v>2611000</v>
       </c>
       <c r="H15" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I15" s="6">
-        <v>2125</v>
+        <v>2105</v>
       </c>
       <c r="J15" s="6">
-        <v>2125</v>
+        <v>2105</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>266</v>
+        <v>244</v>
       </c>
       <c r="L15" s="6">
-        <v>111000</v>
+        <v>76000</v>
       </c>
       <c r="M15" s="6" t="s">
-        <v>267</v>
+        <v>69</v>
       </c>
       <c r="N15" s="6">
-        <v>83000</v>
+        <v>50000</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>268</v>
+        <v>69</v>
       </c>
       <c r="P15" s="6">
-        <v>85000</v>
+        <v>50000</v>
       </c>
       <c r="Q15" s="6" t="s">
-        <v>269</v>
+        <v>245</v>
       </c>
       <c r="R15" s="6" t="s">
-        <v>270</v>
+        <v>246</v>
       </c>
       <c r="S15" s="6" t="s">
         <v>37</v>
       </c>
       <c r="T15" s="6" t="s">
-        <v>271</v>
+        <v>247</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>272</v>
+        <v>248</v>
       </c>
       <c r="V15" s="6" t="s">
-        <v>162</v>
+        <v>249</v>
       </c>
       <c r="W15" s="6" t="s">
-        <v>238</v>
+        <v>250</v>
       </c>
       <c r="X15" s="6" t="s">
-        <v>238</v>
+        <v>93</v>
       </c>
       <c r="Y15" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="Z15" s="6" t="s">
-        <v>63</v>
+        <v>251</v>
       </c>
       <c r="AA15" s="6" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" spans="1:27">
+    <row r="16" s="1" customFormat="1" spans="1:34">
       <c r="A16" s="6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="E16" s="13">
-        <v>44953.7534722222</v>
+        <v>44988.75</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="G16" s="6">
-        <v>3468000</v>
+        <v>3650000</v>
       </c>
       <c r="H16" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I16" s="6">
-        <v>6531</v>
+        <v>2125</v>
       </c>
       <c r="J16" s="6">
-        <v>6531</v>
+        <v>2125</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="L16" s="6">
-        <v>80000</v>
+        <v>111000</v>
       </c>
       <c r="M16" s="6" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="N16" s="6">
-        <v>51000</v>
+        <v>83000</v>
       </c>
       <c r="O16" s="6" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="P16" s="6">
-        <v>57000</v>
+        <v>85000</v>
       </c>
       <c r="Q16" s="6" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="R16" s="6" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="S16" s="6" t="s">
         <v>37</v>
       </c>
       <c r="T16" s="6" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="U16" s="6" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="V16" s="6" t="s">
-        <v>150</v>
+        <v>162</v>
       </c>
       <c r="W16" s="6" t="s">
-        <v>284</v>
+        <v>238</v>
       </c>
       <c r="X16" s="6" t="s">
-        <v>285</v>
+        <v>238</v>
       </c>
       <c r="Y16" s="6" t="s">
-        <v>286</v>
+        <v>62</v>
       </c>
       <c r="Z16" s="6" t="s">
-        <v>287</v>
+        <v>63</v>
       </c>
       <c r="AA16" s="6" t="s">
         <v>60</v>
@@ -11856,82 +11905,82 @@
     </row>
     <row r="17" s="1" customFormat="1" spans="1:27">
       <c r="A17" s="6">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
       <c r="E17" s="13">
-        <v>44939.75</v>
+        <v>44953.7534722222</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="G17" s="6">
-        <v>3875000</v>
+        <v>3468000</v>
       </c>
       <c r="H17" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I17" s="6">
-        <v>5072</v>
+        <v>6531</v>
       </c>
       <c r="J17" s="6">
-        <v>5072</v>
+        <v>6531</v>
       </c>
       <c r="K17" s="6" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
       <c r="L17" s="6">
-        <v>107000</v>
+        <v>80000</v>
       </c>
       <c r="M17" s="6" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="N17" s="6">
-        <v>87000</v>
+        <v>51000</v>
       </c>
       <c r="O17" s="6" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="P17" s="6">
-        <v>80000</v>
+        <v>57000</v>
       </c>
       <c r="Q17" s="6" t="s">
-        <v>294</v>
+        <v>280</v>
       </c>
       <c r="R17" s="6" t="s">
-        <v>295</v>
+        <v>281</v>
       </c>
       <c r="S17" s="6" t="s">
-        <v>296</v>
+        <v>37</v>
       </c>
       <c r="T17" s="6" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="U17" s="6" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
       <c r="V17" s="6" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="W17" s="6" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="X17" s="6" t="s">
-        <v>79</v>
+        <v>285</v>
       </c>
       <c r="Y17" s="6" t="s">
-        <v>62</v>
+        <v>286</v>
       </c>
       <c r="Z17" s="6" t="s">
-        <v>300</v>
+        <v>287</v>
       </c>
       <c r="AA17" s="6" t="s">
         <v>60</v>
@@ -11939,82 +11988,82 @@
     </row>
     <row r="18" s="1" customFormat="1" spans="1:27">
       <c r="A18" s="6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>301</v>
+        <v>288</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>302</v>
+        <v>289</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>303</v>
+        <v>290</v>
       </c>
       <c r="E18" s="13">
-        <v>44863.75</v>
+        <v>44939.75</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>304</v>
+        <v>291</v>
       </c>
       <c r="G18" s="6">
-        <v>4922000</v>
+        <v>3875000</v>
       </c>
       <c r="H18" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I18" s="6">
-        <v>8314</v>
+        <v>5072</v>
       </c>
       <c r="J18" s="6">
-        <v>8314</v>
+        <v>5072</v>
       </c>
       <c r="K18" s="6" t="s">
-        <v>305</v>
+        <v>292</v>
       </c>
       <c r="L18" s="6">
-        <v>127000</v>
+        <v>107000</v>
       </c>
       <c r="M18" s="6" t="s">
-        <v>306</v>
+        <v>293</v>
       </c>
       <c r="N18" s="6">
-        <v>100000</v>
+        <v>87000</v>
       </c>
       <c r="O18" s="6" t="s">
-        <v>307</v>
+        <v>277</v>
       </c>
       <c r="P18" s="6">
-        <v>96000</v>
+        <v>80000</v>
       </c>
       <c r="Q18" s="6" t="s">
-        <v>308</v>
+        <v>294</v>
       </c>
       <c r="R18" s="6" t="s">
-        <v>309</v>
+        <v>295</v>
       </c>
       <c r="S18" s="6" t="s">
-        <v>37</v>
+        <v>296</v>
       </c>
       <c r="T18" s="6" t="s">
-        <v>310</v>
+        <v>297</v>
       </c>
       <c r="U18" s="6" t="s">
-        <v>311</v>
+        <v>298</v>
       </c>
       <c r="V18" s="6" t="s">
-        <v>162</v>
+        <v>122</v>
       </c>
       <c r="W18" s="6" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="X18" s="6" t="s">
-        <v>238</v>
+        <v>79</v>
       </c>
       <c r="Y18" s="6" t="s">
-        <v>286</v>
+        <v>62</v>
       </c>
       <c r="Z18" s="6" t="s">
-        <v>313</v>
+        <v>300</v>
       </c>
       <c r="AA18" s="6" t="s">
         <v>60</v>
@@ -12022,165 +12071,165 @@
     </row>
     <row r="19" s="1" customFormat="1" spans="1:27">
       <c r="A19" s="6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>314</v>
+        <v>301</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>315</v>
+        <v>302</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>316</v>
+        <v>303</v>
       </c>
       <c r="E19" s="13">
-        <v>44785.75</v>
+        <v>44863.75</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>317</v>
+        <v>304</v>
       </c>
       <c r="G19" s="6">
-        <v>1431000</v>
+        <v>4922000</v>
       </c>
       <c r="H19" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I19" s="6">
-        <v>1944</v>
+        <v>8314</v>
       </c>
       <c r="J19" s="6">
-        <v>1944</v>
+        <v>8314</v>
       </c>
       <c r="K19" s="6" t="s">
-        <v>182</v>
+        <v>305</v>
       </c>
       <c r="L19" s="6">
-        <v>54000</v>
+        <v>127000</v>
       </c>
       <c r="M19" s="6" t="s">
-        <v>318</v>
+        <v>306</v>
       </c>
       <c r="N19" s="6">
-        <v>41000</v>
+        <v>100000</v>
       </c>
       <c r="O19" s="6" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="P19" s="6">
-        <v>35000</v>
+        <v>96000</v>
       </c>
       <c r="Q19" s="6" t="s">
-        <v>320</v>
+        <v>308</v>
       </c>
       <c r="R19" s="6" t="s">
-        <v>321</v>
+        <v>309</v>
       </c>
       <c r="S19" s="6" t="s">
         <v>37</v>
       </c>
       <c r="T19" s="6" t="s">
-        <v>37</v>
+        <v>310</v>
       </c>
       <c r="U19" s="6" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="V19" s="6" t="s">
-        <v>323</v>
+        <v>162</v>
       </c>
       <c r="W19" s="6" t="s">
-        <v>136</v>
+        <v>312</v>
       </c>
       <c r="X19" s="6" t="s">
-        <v>109</v>
+        <v>238</v>
       </c>
       <c r="Y19" s="6" t="s">
-        <v>42</v>
+        <v>286</v>
       </c>
       <c r="Z19" s="6" t="s">
-        <v>324</v>
+        <v>313</v>
       </c>
       <c r="AA19" s="6" t="s">
-        <v>325</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20" s="1" customFormat="1" spans="1:27">
       <c r="A20" s="6">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>326</v>
+        <v>314</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>327</v>
+        <v>315</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>328</v>
+        <v>316</v>
       </c>
       <c r="E20" s="13">
-        <v>44694.7503587963</v>
+        <v>44785.75</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>329</v>
+        <v>317</v>
       </c>
       <c r="G20" s="6">
-        <v>3812000</v>
+        <v>1431000</v>
       </c>
       <c r="H20" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I20" s="6">
-        <v>3196</v>
+        <v>1944</v>
       </c>
       <c r="J20" s="6">
-        <v>3196</v>
+        <v>1944</v>
       </c>
       <c r="K20" s="6" t="s">
-        <v>221</v>
+        <v>182</v>
       </c>
       <c r="L20" s="6">
-        <v>108000</v>
+        <v>54000</v>
       </c>
       <c r="M20" s="6" t="s">
-        <v>267</v>
+        <v>318</v>
       </c>
       <c r="N20" s="6">
-        <v>83000</v>
+        <v>41000</v>
       </c>
       <c r="O20" s="6" t="s">
-        <v>330</v>
+        <v>319</v>
       </c>
       <c r="P20" s="6">
-        <v>79000</v>
+        <v>35000</v>
       </c>
       <c r="Q20" s="6" t="s">
-        <v>331</v>
+        <v>320</v>
       </c>
       <c r="R20" s="6" t="s">
-        <v>332</v>
+        <v>321</v>
       </c>
       <c r="S20" s="6" t="s">
         <v>37</v>
       </c>
       <c r="T20" s="6" t="s">
-        <v>282</v>
+        <v>37</v>
       </c>
       <c r="U20" s="6" t="s">
-        <v>333</v>
+        <v>322</v>
       </c>
       <c r="V20" s="6" t="s">
-        <v>334</v>
+        <v>323</v>
       </c>
       <c r="W20" s="6" t="s">
         <v>136</v>
       </c>
       <c r="X20" s="6" t="s">
-        <v>335</v>
+        <v>109</v>
       </c>
       <c r="Y20" s="6" t="s">
         <v>42</v>
       </c>
       <c r="Z20" s="6" t="s">
-        <v>80</v>
+        <v>324</v>
       </c>
       <c r="AA20" s="6" t="s">
         <v>325</v>
@@ -12188,141 +12237,141 @@
     </row>
     <row r="21" s="1" customFormat="1" spans="1:27">
       <c r="A21" s="6">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>346</v>
+        <v>326</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>347</v>
+        <v>327</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>348</v>
+        <v>328</v>
       </c>
       <c r="E21" s="13">
-        <v>44595.7500925926</v>
+        <v>44694.7503587963</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>349</v>
+        <v>329</v>
       </c>
       <c r="G21" s="6">
-        <v>1789000</v>
+        <v>3812000</v>
       </c>
       <c r="H21" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I21" s="6">
-        <v>4545</v>
+        <v>3196</v>
       </c>
       <c r="J21" s="6">
-        <v>4545</v>
+        <v>3196</v>
       </c>
       <c r="K21" s="6" t="s">
-        <v>102</v>
+        <v>221</v>
       </c>
       <c r="L21" s="6">
-        <v>66000</v>
+        <v>108000</v>
       </c>
       <c r="M21" s="6" t="s">
-        <v>103</v>
+        <v>267</v>
       </c>
       <c r="N21" s="6">
-        <v>53000</v>
+        <v>83000</v>
       </c>
       <c r="O21" s="6" t="s">
-        <v>129</v>
+        <v>330</v>
       </c>
       <c r="P21" s="6">
-        <v>44000</v>
+        <v>79000</v>
       </c>
       <c r="Q21" s="6" t="s">
-        <v>350</v>
+        <v>331</v>
       </c>
       <c r="R21" s="6" t="s">
-        <v>351</v>
+        <v>332</v>
       </c>
       <c r="S21" s="6" t="s">
         <v>37</v>
       </c>
       <c r="T21" s="6" t="s">
-        <v>37</v>
+        <v>282</v>
       </c>
       <c r="U21" s="6" t="s">
-        <v>352</v>
+        <v>333</v>
       </c>
       <c r="V21" s="6" t="s">
-        <v>150</v>
+        <v>334</v>
       </c>
       <c r="W21" s="6" t="s">
-        <v>353</v>
+        <v>136</v>
       </c>
       <c r="X21" s="6" t="s">
-        <v>176</v>
+        <v>335</v>
       </c>
       <c r="Y21" s="6" t="s">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c r="Z21" s="6" t="s">
-        <v>354</v>
+        <v>80</v>
       </c>
       <c r="AA21" s="6" t="s">
-        <v>355</v>
+        <v>325</v>
       </c>
     </row>
     <row r="22" s="1" customFormat="1" spans="1:27">
       <c r="A22" s="6">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>356</v>
+        <v>346</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>357</v>
+        <v>347</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>358</v>
+        <v>348</v>
       </c>
       <c r="E22" s="13">
-        <v>44583.75</v>
+        <v>44595.7500925926</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>359</v>
+        <v>349</v>
       </c>
       <c r="G22" s="6">
-        <v>1425000</v>
+        <v>1789000</v>
       </c>
       <c r="H22" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I22" s="6">
-        <v>1317</v>
+        <v>4545</v>
       </c>
       <c r="J22" s="6">
-        <v>1317</v>
+        <v>4545</v>
       </c>
       <c r="K22" s="6" t="s">
-        <v>196</v>
+        <v>102</v>
       </c>
       <c r="L22" s="6">
-        <v>58000</v>
+        <v>66000</v>
       </c>
       <c r="M22" s="6" t="s">
-        <v>360</v>
+        <v>103</v>
       </c>
       <c r="N22" s="6">
-        <v>40000</v>
+        <v>53000</v>
       </c>
       <c r="O22" s="6" t="s">
-        <v>340</v>
+        <v>129</v>
       </c>
       <c r="P22" s="6">
-        <v>36000</v>
+        <v>44000</v>
       </c>
       <c r="Q22" s="6" t="s">
-        <v>361</v>
+        <v>350</v>
       </c>
       <c r="R22" s="6" t="s">
-        <v>362</v>
+        <v>351</v>
       </c>
       <c r="S22" s="6" t="s">
         <v>37</v>
@@ -12331,22 +12380,22 @@
         <v>37</v>
       </c>
       <c r="U22" s="6" t="s">
-        <v>363</v>
+        <v>352</v>
       </c>
       <c r="V22" s="6" t="s">
-        <v>249</v>
+        <v>150</v>
       </c>
       <c r="W22" s="6" t="s">
-        <v>364</v>
+        <v>353</v>
       </c>
       <c r="X22" s="6" t="s">
         <v>176</v>
       </c>
       <c r="Y22" s="6" t="s">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="Z22" s="6" t="s">
-        <v>324</v>
+        <v>354</v>
       </c>
       <c r="AA22" s="6" t="s">
         <v>355</v>
@@ -12354,248 +12403,248 @@
     </row>
     <row r="23" s="1" customFormat="1" spans="1:27">
       <c r="A23" s="6">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>390</v>
+        <v>356</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>391</v>
+        <v>357</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>392</v>
+        <v>358</v>
       </c>
       <c r="E23" s="13">
-        <v>44471.7501851852</v>
+        <v>44583.75</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>393</v>
+        <v>359</v>
       </c>
       <c r="G23" s="6">
-        <v>990000</v>
+        <v>1425000</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="I23" s="6">
-        <v>2129</v>
+        <v>1317</v>
       </c>
       <c r="J23" s="6">
-        <v>2129</v>
+        <v>1317</v>
       </c>
       <c r="K23" s="6" t="s">
-        <v>371</v>
+        <v>196</v>
       </c>
       <c r="L23" s="6">
-        <v>48000</v>
+        <v>58000</v>
       </c>
       <c r="M23" s="6" t="s">
-        <v>71</v>
+        <v>360</v>
       </c>
       <c r="N23" s="6">
-        <v>30000</v>
+        <v>40000</v>
       </c>
       <c r="O23" s="6" t="s">
-        <v>394</v>
+        <v>340</v>
       </c>
       <c r="P23" s="6">
-        <v>26000</v>
+        <v>36000</v>
       </c>
       <c r="Q23" s="6" t="s">
-        <v>395</v>
+        <v>361</v>
       </c>
       <c r="R23" s="6" t="s">
-        <v>396</v>
+        <v>362</v>
       </c>
       <c r="S23" s="6" t="s">
         <v>37</v>
       </c>
       <c r="T23" s="6" t="s">
-        <v>397</v>
+        <v>37</v>
       </c>
       <c r="U23" s="6" t="s">
-        <v>398</v>
+        <v>363</v>
       </c>
       <c r="V23" s="6" t="s">
-        <v>399</v>
+        <v>249</v>
       </c>
       <c r="W23" s="6" t="s">
-        <v>400</v>
+        <v>364</v>
       </c>
       <c r="X23" s="6" t="s">
-        <v>400</v>
+        <v>176</v>
       </c>
       <c r="Y23" s="6" t="s">
         <v>94</v>
       </c>
       <c r="Z23" s="6" t="s">
-        <v>80</v>
+        <v>324</v>
       </c>
       <c r="AA23" s="6" t="s">
-        <v>378</v>
+        <v>355</v>
       </c>
     </row>
     <row r="24" s="1" customFormat="1" spans="1:27">
       <c r="A24" s="6">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>401</v>
+        <v>390</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>402</v>
+        <v>391</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>403</v>
+        <v>392</v>
       </c>
       <c r="E24" s="13">
-        <v>44449.7500462963</v>
+        <v>44471.7501851852</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>404</v>
+        <v>393</v>
       </c>
       <c r="G24" s="6">
-        <v>1673000</v>
+        <v>990000</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="I24" s="6">
-        <v>1840</v>
+        <v>2129</v>
       </c>
       <c r="J24" s="6">
-        <v>1840</v>
+        <v>2129</v>
       </c>
       <c r="K24" s="6" t="s">
-        <v>88</v>
+        <v>371</v>
       </c>
       <c r="L24" s="6">
-        <v>75000</v>
+        <v>48000</v>
       </c>
       <c r="M24" s="6" t="s">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="N24" s="6">
-        <v>53000</v>
+        <v>30000</v>
       </c>
       <c r="O24" s="6" t="s">
-        <v>405</v>
+        <v>394</v>
       </c>
       <c r="P24" s="6">
-        <v>45000</v>
+        <v>26000</v>
       </c>
       <c r="Q24" s="6" t="s">
-        <v>406</v>
+        <v>395</v>
       </c>
       <c r="R24" s="6" t="s">
-        <v>407</v>
+        <v>396</v>
       </c>
       <c r="S24" s="6" t="s">
-        <v>408</v>
+        <v>37</v>
       </c>
       <c r="T24" s="6" t="s">
-        <v>409</v>
+        <v>397</v>
       </c>
       <c r="U24" s="6" t="s">
-        <v>410</v>
+        <v>398</v>
       </c>
       <c r="V24" s="6" t="s">
-        <v>411</v>
+        <v>399</v>
       </c>
       <c r="W24" s="6" t="s">
-        <v>136</v>
+        <v>400</v>
       </c>
       <c r="X24" s="6" t="s">
-        <v>412</v>
+        <v>400</v>
       </c>
       <c r="Y24" s="6" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="Z24" s="6" t="s">
         <v>80</v>
       </c>
       <c r="AA24" s="6" t="s">
-        <v>413</v>
+        <v>378</v>
       </c>
     </row>
     <row r="25" s="1" customFormat="1" spans="1:27">
       <c r="A25" s="6">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>414</v>
+        <v>401</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>415</v>
+        <v>402</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>416</v>
+        <v>403</v>
       </c>
       <c r="E25" s="13">
-        <v>44421.7501736111</v>
+        <v>44449.7500462963</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>417</v>
+        <v>404</v>
       </c>
       <c r="G25" s="6">
-        <v>4794000</v>
+        <v>1673000</v>
       </c>
       <c r="H25" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="I25" s="6" t="s">
-        <v>383</v>
+      <c r="I25" s="6">
+        <v>1840</v>
       </c>
       <c r="J25" s="6">
-        <v>16000</v>
+        <v>1840</v>
       </c>
       <c r="K25" s="6" t="s">
-        <v>418</v>
+        <v>88</v>
       </c>
       <c r="L25" s="6">
-        <v>143000</v>
+        <v>75000</v>
       </c>
       <c r="M25" s="6" t="s">
-        <v>419</v>
+        <v>103</v>
       </c>
       <c r="N25" s="6">
-        <v>109000</v>
+        <v>53000</v>
       </c>
       <c r="O25" s="6" t="s">
-        <v>266</v>
+        <v>405</v>
       </c>
       <c r="P25" s="6">
-        <v>111000</v>
+        <v>45000</v>
       </c>
       <c r="Q25" s="6" t="s">
-        <v>420</v>
+        <v>406</v>
       </c>
       <c r="R25" s="6" t="s">
-        <v>421</v>
+        <v>407</v>
       </c>
       <c r="S25" s="6" t="s">
-        <v>37</v>
+        <v>408</v>
       </c>
       <c r="T25" s="6" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="U25" s="6" t="s">
-        <v>423</v>
+        <v>410</v>
       </c>
       <c r="V25" s="6" t="s">
-        <v>424</v>
+        <v>411</v>
       </c>
       <c r="W25" s="6" t="s">
-        <v>425</v>
+        <v>136</v>
       </c>
       <c r="X25" s="6" t="s">
-        <v>109</v>
+        <v>412</v>
       </c>
       <c r="Y25" s="6" t="s">
-        <v>426</v>
+        <v>62</v>
       </c>
       <c r="Z25" s="6" t="s">
-        <v>427</v>
+        <v>80</v>
       </c>
       <c r="AA25" s="6" t="s">
         <v>413</v>
@@ -12603,165 +12652,165 @@
     </row>
     <row r="26" s="1" customFormat="1" spans="1:27">
       <c r="A26" s="6">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>428</v>
+        <v>414</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>429</v>
+        <v>415</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>430</v>
+        <v>416</v>
       </c>
       <c r="E26" s="13">
-        <v>44316.7501388889</v>
+        <v>44421.7501736111</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>431</v>
+        <v>417</v>
       </c>
       <c r="G26" s="6">
-        <v>3807000</v>
+        <v>4794000</v>
       </c>
       <c r="H26" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="I26" s="6">
-        <v>3670</v>
+      <c r="I26" s="6" t="s">
+        <v>383</v>
       </c>
       <c r="J26" s="6">
-        <v>3670</v>
+        <v>16000</v>
       </c>
       <c r="K26" s="6" t="s">
-        <v>432</v>
+        <v>418</v>
       </c>
       <c r="L26" s="6">
-        <v>122000</v>
+        <v>143000</v>
       </c>
       <c r="M26" s="6" t="s">
-        <v>433</v>
+        <v>419</v>
       </c>
       <c r="N26" s="6">
-        <v>81000</v>
+        <v>109000</v>
       </c>
       <c r="O26" s="6" t="s">
-        <v>434</v>
+        <v>266</v>
       </c>
       <c r="P26" s="6">
-        <v>94000</v>
+        <v>111000</v>
       </c>
       <c r="Q26" s="6" t="s">
-        <v>435</v>
+        <v>420</v>
       </c>
       <c r="R26" s="6" t="s">
-        <v>436</v>
+        <v>421</v>
       </c>
       <c r="S26" s="6" t="s">
         <v>37</v>
       </c>
       <c r="T26" s="6" t="s">
-        <v>37</v>
+        <v>422</v>
       </c>
       <c r="U26" s="6" t="s">
-        <v>437</v>
+        <v>423</v>
       </c>
       <c r="V26" s="6" t="s">
-        <v>150</v>
+        <v>424</v>
       </c>
       <c r="W26" s="6" t="s">
-        <v>438</v>
+        <v>425</v>
       </c>
       <c r="X26" s="6" t="s">
-        <v>439</v>
+        <v>109</v>
       </c>
       <c r="Y26" s="6" t="s">
-        <v>62</v>
+        <v>426</v>
       </c>
       <c r="Z26" s="6" t="s">
-        <v>354</v>
+        <v>427</v>
       </c>
       <c r="AA26" s="6" t="s">
-        <v>440</v>
+        <v>413</v>
       </c>
     </row>
     <row r="27" s="1" customFormat="1" spans="1:27">
       <c r="A27" s="6">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>441</v>
+        <v>428</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>442</v>
+        <v>429</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>443</v>
+        <v>430</v>
       </c>
       <c r="E27" s="13">
-        <v>44288.7500578704</v>
+        <v>44316.7501388889</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>444</v>
+        <v>431</v>
       </c>
       <c r="G27" s="6">
-        <v>4058000</v>
+        <v>3807000</v>
       </c>
       <c r="H27" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I27" s="6">
-        <v>4115</v>
+        <v>3670</v>
       </c>
       <c r="J27" s="6">
-        <v>4115</v>
+        <v>3670</v>
       </c>
       <c r="K27" s="6" t="s">
-        <v>445</v>
+        <v>432</v>
       </c>
       <c r="L27" s="6">
-        <v>136000</v>
+        <v>122000</v>
       </c>
       <c r="M27" s="6" t="s">
-        <v>306</v>
+        <v>433</v>
       </c>
       <c r="N27" s="6">
-        <v>100000</v>
+        <v>81000</v>
       </c>
       <c r="O27" s="6" t="s">
-        <v>446</v>
+        <v>434</v>
       </c>
       <c r="P27" s="6">
-        <v>95000</v>
+        <v>94000</v>
       </c>
       <c r="Q27" s="6" t="s">
-        <v>447</v>
+        <v>435</v>
       </c>
       <c r="R27" s="6" t="s">
-        <v>448</v>
+        <v>436</v>
       </c>
       <c r="S27" s="6" t="s">
         <v>37</v>
       </c>
       <c r="T27" s="6" t="s">
-        <v>282</v>
+        <v>37</v>
       </c>
       <c r="U27" s="6" t="s">
-        <v>449</v>
+        <v>437</v>
       </c>
       <c r="V27" s="6" t="s">
-        <v>450</v>
+        <v>150</v>
       </c>
       <c r="W27" s="6" t="s">
-        <v>451</v>
+        <v>438</v>
       </c>
       <c r="X27" s="6" t="s">
-        <v>109</v>
+        <v>439</v>
       </c>
       <c r="Y27" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="Z27" s="6" t="s">
-        <v>80</v>
+        <v>354</v>
       </c>
       <c r="AA27" s="6" t="s">
         <v>440</v>
@@ -12769,76 +12818,76 @@
     </row>
     <row r="28" s="1" customFormat="1" spans="1:27">
       <c r="A28" s="6">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="E28" s="13">
-        <v>44267.7501273148</v>
+        <v>44288.7500578704</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="G28" s="6">
-        <v>5615000</v>
+        <v>4058000</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>207</v>
+        <v>49</v>
       </c>
       <c r="I28" s="6">
-        <v>6956</v>
+        <v>4115</v>
       </c>
       <c r="J28" s="6">
-        <v>6956</v>
+        <v>4115</v>
       </c>
       <c r="K28" s="6" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="L28" s="6">
-        <v>196000</v>
+        <v>136000</v>
       </c>
       <c r="M28" s="6" t="s">
-        <v>220</v>
+        <v>306</v>
       </c>
       <c r="N28" s="6">
-        <v>148000</v>
+        <v>100000</v>
       </c>
       <c r="O28" s="6" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="P28" s="6">
-        <v>146000</v>
+        <v>95000</v>
       </c>
       <c r="Q28" s="6" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="R28" s="6" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="S28" s="6" t="s">
         <v>37</v>
       </c>
       <c r="T28" s="6" t="s">
-        <v>460</v>
+        <v>282</v>
       </c>
       <c r="U28" s="6" t="s">
-        <v>657</v>
+        <v>449</v>
       </c>
       <c r="V28" s="6" t="s">
-        <v>150</v>
+        <v>450</v>
       </c>
       <c r="W28" s="6" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="X28" s="6" t="s">
-        <v>463</v>
+        <v>109</v>
       </c>
       <c r="Y28" s="6" t="s">
         <v>42</v>
@@ -12852,82 +12901,82 @@
     </row>
     <row r="29" s="1" customFormat="1" spans="1:27">
       <c r="A29" s="6">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>480</v>
+        <v>452</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>481</v>
+        <v>453</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>482</v>
+        <v>454</v>
       </c>
       <c r="E29" s="13">
-        <v>44197.7500925926</v>
+        <v>44267.7501273148</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>483</v>
+        <v>455</v>
       </c>
       <c r="G29" s="6">
-        <v>2086000</v>
+        <v>5615000</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>49</v>
+        <v>207</v>
       </c>
       <c r="I29" s="6">
-        <v>2152</v>
+        <v>6956</v>
       </c>
       <c r="J29" s="6">
-        <v>2152</v>
+        <v>6956</v>
       </c>
       <c r="K29" s="6" t="s">
-        <v>244</v>
+        <v>456</v>
       </c>
       <c r="L29" s="6">
-        <v>76000</v>
+        <v>196000</v>
       </c>
       <c r="M29" s="6" t="s">
-        <v>484</v>
+        <v>220</v>
       </c>
       <c r="N29" s="6">
-        <v>56000</v>
+        <v>148000</v>
       </c>
       <c r="O29" s="6" t="s">
-        <v>231</v>
+        <v>457</v>
       </c>
       <c r="P29" s="6">
-        <v>52000</v>
+        <v>146000</v>
       </c>
       <c r="Q29" s="6" t="s">
-        <v>485</v>
+        <v>458</v>
       </c>
       <c r="R29" s="6" t="s">
-        <v>486</v>
+        <v>459</v>
       </c>
       <c r="S29" s="6" t="s">
         <v>37</v>
       </c>
       <c r="T29" s="6" t="s">
-        <v>487</v>
+        <v>460</v>
       </c>
       <c r="U29" s="6" t="s">
-        <v>488</v>
+        <v>661</v>
       </c>
       <c r="V29" s="6" t="s">
-        <v>249</v>
+        <v>150</v>
       </c>
       <c r="W29" s="6" t="s">
-        <v>438</v>
+        <v>462</v>
       </c>
       <c r="X29" s="6" t="s">
-        <v>439</v>
+        <v>463</v>
       </c>
       <c r="Y29" s="6" t="s">
-        <v>489</v>
+        <v>42</v>
       </c>
       <c r="Z29" s="6" t="s">
-        <v>490</v>
+        <v>80</v>
       </c>
       <c r="AA29" s="6" t="s">
         <v>440</v>
@@ -12935,82 +12984,82 @@
     </row>
     <row r="30" s="1" customFormat="1" spans="1:27">
       <c r="A30" s="6">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>499</v>
+        <v>480</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>500</v>
+        <v>481</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>501</v>
+        <v>482</v>
       </c>
       <c r="E30" s="13">
-        <v>44141.7502893518</v>
+        <v>44197.7500925926</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>502</v>
+        <v>483</v>
       </c>
       <c r="G30" s="6">
-        <v>2142000</v>
+        <v>2086000</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I30" s="6">
-        <v>3466</v>
+        <v>2152</v>
       </c>
       <c r="J30" s="6">
-        <v>3466</v>
+        <v>2152</v>
       </c>
       <c r="K30" s="6" t="s">
-        <v>268</v>
+        <v>244</v>
       </c>
       <c r="L30" s="6">
-        <v>85000</v>
+        <v>76000</v>
       </c>
       <c r="M30" s="6" t="s">
-        <v>102</v>
+        <v>484</v>
       </c>
       <c r="N30" s="6">
-        <v>66000</v>
+        <v>56000</v>
       </c>
       <c r="O30" s="6" t="s">
-        <v>195</v>
+        <v>231</v>
       </c>
       <c r="P30" s="6">
-        <v>59000</v>
+        <v>52000</v>
       </c>
       <c r="Q30" s="6" t="s">
-        <v>503</v>
+        <v>485</v>
       </c>
       <c r="R30" s="6" t="s">
-        <v>504</v>
+        <v>486</v>
       </c>
       <c r="S30" s="6" t="s">
         <v>37</v>
       </c>
       <c r="T30" s="6" t="s">
-        <v>505</v>
+        <v>487</v>
       </c>
       <c r="U30" s="6" t="s">
-        <v>506</v>
+        <v>488</v>
       </c>
       <c r="V30" s="6" t="s">
-        <v>450</v>
+        <v>249</v>
       </c>
       <c r="W30" s="6" t="s">
-        <v>136</v>
+        <v>438</v>
       </c>
       <c r="X30" s="6" t="s">
-        <v>109</v>
+        <v>439</v>
       </c>
       <c r="Y30" s="6" t="s">
-        <v>62</v>
+        <v>489</v>
       </c>
       <c r="Z30" s="6" t="s">
-        <v>324</v>
+        <v>490</v>
       </c>
       <c r="AA30" s="6" t="s">
         <v>440</v>
@@ -13018,82 +13067,82 @@
     </row>
     <row r="31" s="1" customFormat="1" spans="1:27">
       <c r="A31" s="6">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>517</v>
+        <v>499</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>518</v>
+        <v>500</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>519</v>
+        <v>501</v>
       </c>
       <c r="E31" s="13">
-        <v>44057.7502199074</v>
+        <v>44141.7502893518</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>520</v>
+        <v>502</v>
       </c>
       <c r="G31" s="6">
-        <v>4293000</v>
+        <v>2142000</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="I31" s="6" t="s">
-        <v>469</v>
+      <c r="I31" s="6">
+        <v>3466</v>
       </c>
       <c r="J31" s="6">
-        <v>13000</v>
+        <v>3466</v>
       </c>
       <c r="K31" s="6" t="s">
-        <v>86</v>
+        <v>268</v>
       </c>
       <c r="L31" s="6">
-        <v>132000</v>
+        <v>85000</v>
       </c>
       <c r="M31" s="6" t="s">
-        <v>521</v>
+        <v>102</v>
       </c>
       <c r="N31" s="6">
-        <v>110000</v>
+        <v>66000</v>
       </c>
       <c r="O31" s="6" t="s">
-        <v>258</v>
+        <v>195</v>
       </c>
       <c r="P31" s="6">
-        <v>98000</v>
+        <v>59000</v>
       </c>
       <c r="Q31" s="6" t="s">
-        <v>522</v>
+        <v>503</v>
       </c>
       <c r="R31" s="6" t="s">
-        <v>523</v>
+        <v>504</v>
       </c>
       <c r="S31" s="6" t="s">
         <v>37</v>
       </c>
       <c r="T31" s="6" t="s">
-        <v>37</v>
+        <v>505</v>
       </c>
       <c r="U31" s="6" t="s">
-        <v>524</v>
+        <v>506</v>
       </c>
       <c r="V31" s="6" t="s">
-        <v>525</v>
+        <v>450</v>
       </c>
       <c r="W31" s="6" t="s">
-        <v>438</v>
+        <v>136</v>
       </c>
       <c r="X31" s="6" t="s">
-        <v>285</v>
+        <v>109</v>
       </c>
       <c r="Y31" s="6" t="s">
-        <v>42</v>
+        <v>62</v>
       </c>
       <c r="Z31" s="6" t="s">
-        <v>80</v>
+        <v>324</v>
       </c>
       <c r="AA31" s="6" t="s">
         <v>440</v>
@@ -13101,82 +13150,82 @@
     </row>
     <row r="32" s="1" customFormat="1" spans="1:27">
       <c r="A32" s="6">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="E32" s="13">
-        <v>43994.7709143519</v>
+        <v>44057.7502199074</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="G32" s="6">
-        <v>2393000</v>
+        <v>4293000</v>
       </c>
       <c r="H32" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="I32" s="6">
-        <v>4707</v>
+      <c r="I32" s="6" t="s">
+        <v>469</v>
       </c>
       <c r="J32" s="6">
-        <v>4707</v>
+        <v>13000</v>
       </c>
       <c r="K32" s="6" t="s">
-        <v>156</v>
+        <v>86</v>
       </c>
       <c r="L32" s="6">
-        <v>97000</v>
+        <v>132000</v>
       </c>
       <c r="M32" s="6" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="N32" s="6">
-        <v>73000</v>
+        <v>110000</v>
       </c>
       <c r="O32" s="6" t="s">
-        <v>531</v>
+        <v>258</v>
       </c>
       <c r="P32" s="6">
-        <v>72000</v>
+        <v>98000</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="R32" s="6" t="s">
-        <v>533</v>
+        <v>523</v>
       </c>
       <c r="S32" s="6" t="s">
         <v>37</v>
       </c>
       <c r="T32" s="6" t="s">
-        <v>199</v>
+        <v>37</v>
       </c>
       <c r="U32" s="6" t="s">
-        <v>534</v>
+        <v>524</v>
       </c>
       <c r="V32" s="6" t="s">
-        <v>92</v>
+        <v>525</v>
       </c>
       <c r="W32" s="6" t="s">
-        <v>535</v>
+        <v>438</v>
       </c>
       <c r="X32" s="6" t="s">
-        <v>479</v>
+        <v>285</v>
       </c>
       <c r="Y32" s="6" t="s">
         <v>42</v>
       </c>
       <c r="Z32" s="6" t="s">
-        <v>536</v>
+        <v>80</v>
       </c>
       <c r="AA32" s="6" t="s">
         <v>440</v>
@@ -13184,163 +13233,163 @@
     </row>
     <row r="33" s="1" customFormat="1" spans="1:27">
       <c r="A33" s="6">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>537</v>
+        <v>526</v>
       </c>
       <c r="C33" s="6" t="s">
-        <v>538</v>
+        <v>527</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>539</v>
+        <v>528</v>
       </c>
       <c r="E33" s="13">
-        <v>43922.4173611111</v>
+        <v>43994.7709143519</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>540</v>
+        <v>529</v>
       </c>
       <c r="G33" s="6">
-        <v>9869000</v>
+        <v>2393000</v>
       </c>
       <c r="H33" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>541</v>
+        <v>49</v>
+      </c>
+      <c r="I33" s="6">
+        <v>4707</v>
       </c>
       <c r="J33" s="6">
-        <v>23000</v>
+        <v>4707</v>
       </c>
       <c r="K33" s="6" t="s">
-        <v>542</v>
+        <v>156</v>
       </c>
       <c r="L33" s="6">
-        <v>418000</v>
+        <v>97000</v>
       </c>
       <c r="M33" s="6" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="N33" s="6">
-        <v>278000</v>
+        <v>73000</v>
       </c>
       <c r="O33" s="6" t="s">
-        <v>544</v>
+        <v>531</v>
       </c>
       <c r="P33" s="6">
-        <v>306000</v>
+        <v>72000</v>
       </c>
       <c r="Q33" s="6" t="s">
-        <v>545</v>
+        <v>532</v>
       </c>
       <c r="R33" s="6" t="s">
-        <v>546</v>
+        <v>533</v>
       </c>
       <c r="S33" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="T33" s="6"/>
+      <c r="T33" s="6" t="s">
+        <v>199</v>
+      </c>
       <c r="U33" s="6" t="s">
-        <v>547</v>
+        <v>534</v>
       </c>
       <c r="V33" s="6" t="s">
-        <v>249</v>
+        <v>92</v>
       </c>
       <c r="W33" s="6" t="s">
-        <v>438</v>
+        <v>535</v>
       </c>
       <c r="X33" s="6" t="s">
-        <v>109</v>
+        <v>479</v>
       </c>
       <c r="Y33" s="6" t="s">
         <v>42</v>
       </c>
       <c r="Z33" s="6" t="s">
-        <v>324</v>
+        <v>536</v>
       </c>
       <c r="AA33" s="6" t="s">
-        <v>548</v>
+        <v>440</v>
       </c>
     </row>
     <row r="34" s="1" customFormat="1" spans="1:27">
       <c r="A34" s="6">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B34" s="6" t="s">
-        <v>549</v>
+        <v>537</v>
       </c>
       <c r="C34" s="6" t="s">
-        <v>550</v>
+        <v>538</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>551</v>
+        <v>539</v>
       </c>
       <c r="E34" s="13">
-        <v>43813.4970949074</v>
+        <v>43922.4173611111</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>552</v>
+        <v>540</v>
       </c>
       <c r="G34" s="6">
-        <v>2458000</v>
+        <v>9869000</v>
       </c>
       <c r="H34" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="I34" s="6">
-        <v>5941</v>
+        <v>207</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>541</v>
       </c>
       <c r="J34" s="6">
-        <v>5941</v>
+        <v>23000</v>
       </c>
       <c r="K34" s="6" t="s">
-        <v>553</v>
+        <v>542</v>
       </c>
       <c r="L34" s="6">
-        <v>99000</v>
+        <v>418000</v>
       </c>
       <c r="M34" s="6" t="s">
-        <v>277</v>
+        <v>543</v>
       </c>
       <c r="N34" s="6">
-        <v>80000</v>
+        <v>278000</v>
       </c>
       <c r="O34" s="6" t="s">
-        <v>277</v>
+        <v>544</v>
       </c>
       <c r="P34" s="6">
-        <v>80000</v>
+        <v>306000</v>
       </c>
       <c r="Q34" s="6" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="R34" s="6" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
       <c r="S34" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="T34" s="6" t="s">
-        <v>556</v>
-      </c>
+      <c r="T34" s="6"/>
       <c r="U34" s="6" t="s">
-        <v>557</v>
+        <v>547</v>
       </c>
       <c r="V34" s="6" t="s">
-        <v>122</v>
+        <v>249</v>
       </c>
       <c r="W34" s="6" t="s">
-        <v>462</v>
+        <v>438</v>
       </c>
       <c r="X34" s="6" t="s">
-        <v>462</v>
+        <v>109</v>
       </c>
       <c r="Y34" s="6" t="s">
         <v>42</v>
       </c>
       <c r="Z34" s="6" t="s">
-        <v>558</v>
+        <v>324</v>
       </c>
       <c r="AA34" s="6" t="s">
         <v>548</v>
@@ -13348,165 +13397,165 @@
     </row>
     <row r="35" s="1" customFormat="1" spans="1:27">
       <c r="A35" s="6">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B35" s="6" t="s">
-        <v>559</v>
+        <v>549</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>560</v>
+        <v>550</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>561</v>
+        <v>551</v>
       </c>
       <c r="E35" s="13">
-        <v>43707.7503587963</v>
+        <v>43813.4970949074</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="G35" s="6">
-        <v>6286000</v>
+        <v>2458000</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>384</v>
+        <v>49</v>
+      </c>
+      <c r="I35" s="6">
+        <v>5941</v>
       </c>
       <c r="J35" s="6">
-        <v>18000</v>
+        <v>5941</v>
       </c>
       <c r="K35" s="6" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="L35" s="6">
-        <v>215000</v>
+        <v>99000</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>564</v>
+        <v>277</v>
       </c>
       <c r="N35" s="6">
-        <v>190000</v>
+        <v>80000</v>
       </c>
       <c r="O35" s="6" t="s">
-        <v>565</v>
+        <v>277</v>
       </c>
       <c r="P35" s="6">
-        <v>173000</v>
+        <v>80000</v>
       </c>
       <c r="Q35" s="6" t="s">
-        <v>566</v>
+        <v>554</v>
       </c>
       <c r="R35" s="6" t="s">
-        <v>567</v>
+        <v>555</v>
       </c>
       <c r="S35" s="6" t="s">
         <v>37</v>
       </c>
       <c r="T35" s="6" t="s">
-        <v>568</v>
+        <v>556</v>
       </c>
       <c r="U35" s="6" t="s">
-        <v>569</v>
+        <v>557</v>
       </c>
       <c r="V35" s="6" t="s">
-        <v>249</v>
+        <v>122</v>
       </c>
       <c r="W35" s="6" t="s">
-        <v>570</v>
+        <v>462</v>
       </c>
       <c r="X35" s="6" t="s">
-        <v>479</v>
+        <v>462</v>
       </c>
       <c r="Y35" s="6" t="s">
         <v>42</v>
       </c>
       <c r="Z35" s="6" t="s">
-        <v>80</v>
+        <v>558</v>
       </c>
       <c r="AA35" s="6" t="s">
         <v>548</v>
       </c>
     </row>
-    <row r="36" spans="1:27">
+    <row r="36" s="1" customFormat="1" spans="1:27">
       <c r="A36" s="6">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B36" s="6" t="s">
-        <v>571</v>
+        <v>559</v>
       </c>
       <c r="C36" s="6" t="s">
-        <v>572</v>
+        <v>560</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>573</v>
+        <v>561</v>
       </c>
       <c r="E36" s="13">
-        <v>43653.8130671296</v>
+        <v>43707.7503587963</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>574</v>
+        <v>562</v>
       </c>
       <c r="G36" s="6">
-        <v>913000</v>
+        <v>6286000</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="I36" s="6">
-        <v>2365</v>
+        <v>207</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>384</v>
       </c>
       <c r="J36" s="6">
-        <v>2365</v>
+        <v>18000</v>
       </c>
       <c r="K36" s="6" t="s">
-        <v>405</v>
+        <v>563</v>
       </c>
       <c r="L36" s="6">
-        <v>45000</v>
+        <v>215000</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>575</v>
+        <v>564</v>
       </c>
       <c r="N36" s="6">
-        <v>32000</v>
+        <v>190000</v>
       </c>
       <c r="O36" s="6" t="s">
-        <v>32</v>
+        <v>565</v>
       </c>
       <c r="P36" s="6">
-        <v>33000</v>
+        <v>173000</v>
       </c>
       <c r="Q36" s="6" t="s">
-        <v>576</v>
+        <v>566</v>
       </c>
       <c r="R36" s="6" t="s">
-        <v>577</v>
+        <v>567</v>
       </c>
       <c r="S36" s="6" t="s">
         <v>37</v>
       </c>
       <c r="T36" s="6" t="s">
-        <v>37</v>
+        <v>568</v>
       </c>
       <c r="U36" s="6" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="V36" s="6" t="s">
-        <v>411</v>
+        <v>249</v>
       </c>
       <c r="W36" s="6" t="s">
-        <v>136</v>
+        <v>570</v>
       </c>
       <c r="X36" s="6" t="s">
-        <v>388</v>
+        <v>479</v>
       </c>
       <c r="Y36" s="6" t="s">
-        <v>579</v>
+        <v>42</v>
       </c>
       <c r="Z36" s="6" t="s">
-        <v>580</v>
+        <v>80</v>
       </c>
       <c r="AA36" s="6" t="s">
         <v>548</v>
@@ -13514,58 +13563,58 @@
     </row>
     <row r="37" spans="1:27">
       <c r="A37" s="6">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B37" s="6" t="s">
-        <v>581</v>
+        <v>571</v>
       </c>
       <c r="C37" s="6" t="s">
-        <v>582</v>
+        <v>572</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>583</v>
+        <v>573</v>
       </c>
       <c r="E37" s="13">
-        <v>43560.521412037</v>
+        <v>43653.8130671296</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>584</v>
+        <v>574</v>
       </c>
       <c r="G37" s="6">
-        <v>2373000</v>
+        <v>913000</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="I37" s="6">
-        <v>5736</v>
+        <v>2365</v>
       </c>
       <c r="J37" s="6">
-        <v>5736</v>
+        <v>2365</v>
       </c>
       <c r="K37" s="6" t="s">
-        <v>258</v>
+        <v>405</v>
       </c>
       <c r="L37" s="6">
-        <v>98000</v>
+        <v>45000</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>530</v>
+        <v>575</v>
       </c>
       <c r="N37" s="6">
-        <v>73000</v>
+        <v>32000</v>
       </c>
       <c r="O37" s="6" t="s">
-        <v>244</v>
+        <v>32</v>
       </c>
       <c r="P37" s="6">
-        <v>76000</v>
+        <v>33000</v>
       </c>
       <c r="Q37" s="6" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="R37" s="6" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="S37" s="6" t="s">
         <v>37</v>
@@ -13574,81 +13623,81 @@
         <v>37</v>
       </c>
       <c r="U37" s="6" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="V37" s="6" t="s">
-        <v>150</v>
+        <v>411</v>
       </c>
       <c r="W37" s="6" t="s">
-        <v>175</v>
+        <v>136</v>
       </c>
       <c r="X37" s="6" t="s">
-        <v>588</v>
+        <v>388</v>
       </c>
       <c r="Y37" s="6" t="s">
         <v>579</v>
       </c>
       <c r="Z37" s="6" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="AA37" s="6" t="s">
-        <v>438</v>
+        <v>548</v>
       </c>
     </row>
     <row r="38" spans="1:27">
       <c r="A38" s="6">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>590</v>
+        <v>581</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="E38" s="13">
-        <v>43497.7596296296</v>
+        <v>43560.521412037</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="G38" s="6">
-        <v>1950000</v>
+        <v>2373000</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I38" s="6">
-        <v>9823</v>
+        <v>5736</v>
       </c>
       <c r="J38" s="6">
-        <v>9823</v>
+        <v>5736</v>
       </c>
       <c r="K38" s="6" t="s">
-        <v>594</v>
+        <v>258</v>
       </c>
       <c r="L38" s="6">
-        <v>90000</v>
+        <v>98000</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="N38" s="6">
-        <v>72000</v>
+        <v>73000</v>
       </c>
       <c r="O38" s="6" t="s">
-        <v>595</v>
+        <v>244</v>
       </c>
       <c r="P38" s="6">
-        <v>63000</v>
+        <v>76000</v>
       </c>
       <c r="Q38" s="6" t="s">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="R38" s="6" t="s">
-        <v>597</v>
+        <v>586</v>
       </c>
       <c r="S38" s="6" t="s">
         <v>37</v>
@@ -13657,22 +13706,22 @@
         <v>37</v>
       </c>
       <c r="U38" s="6" t="s">
-        <v>598</v>
+        <v>587</v>
       </c>
       <c r="V38" s="6" t="s">
-        <v>411</v>
+        <v>150</v>
       </c>
       <c r="W38" s="6" t="s">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="X38" s="6" t="s">
-        <v>109</v>
+        <v>588</v>
       </c>
       <c r="Y38" s="6" t="s">
         <v>579</v>
       </c>
       <c r="Z38" s="6" t="s">
-        <v>599</v>
+        <v>589</v>
       </c>
       <c r="AA38" s="6" t="s">
         <v>438</v>
@@ -13680,58 +13729,58 @@
     </row>
     <row r="39" spans="1:27">
       <c r="A39" s="6">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B39" s="6" t="s">
-        <v>600</v>
+        <v>590</v>
       </c>
       <c r="C39" s="6" t="s">
-        <v>601</v>
+        <v>591</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>602</v>
+        <v>592</v>
       </c>
       <c r="E39" s="13">
-        <v>43427.7481944444</v>
+        <v>43497.7596296296</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>603</v>
+        <v>593</v>
       </c>
       <c r="G39" s="6">
-        <v>1031000</v>
+        <v>1950000</v>
       </c>
       <c r="H39" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I39" s="6">
-        <v>2200</v>
+        <v>9823</v>
       </c>
       <c r="J39" s="6">
-        <v>2200</v>
+        <v>9823</v>
       </c>
       <c r="K39" s="6" t="s">
-        <v>370</v>
+        <v>594</v>
       </c>
       <c r="L39" s="6">
-        <v>47000</v>
+        <v>90000</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>360</v>
+        <v>531</v>
       </c>
       <c r="N39" s="6">
-        <v>40000</v>
+        <v>72000</v>
       </c>
       <c r="O39" s="6" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="P39" s="6">
-        <v>38000</v>
+        <v>63000</v>
       </c>
       <c r="Q39" s="6" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="R39" s="6" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="S39" s="6" t="s">
         <v>37</v>
@@ -13740,13 +13789,13 @@
         <v>37</v>
       </c>
       <c r="U39" s="6" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="V39" s="6" t="s">
-        <v>150</v>
+        <v>411</v>
       </c>
       <c r="W39" s="6" t="s">
-        <v>353</v>
+        <v>136</v>
       </c>
       <c r="X39" s="6" t="s">
         <v>109</v>
@@ -13763,58 +13812,58 @@
     </row>
     <row r="40" spans="1:27">
       <c r="A40" s="6">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B40" s="6" t="s">
-        <v>608</v>
+        <v>600</v>
       </c>
       <c r="C40" s="6" t="s">
-        <v>609</v>
+        <v>601</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>610</v>
+        <v>602</v>
       </c>
       <c r="E40" s="13">
-        <v>43392.7518402778</v>
+        <v>43427.7481944444</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="G40" s="6">
-        <v>1869000</v>
+        <v>1031000</v>
       </c>
       <c r="H40" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I40" s="6">
-        <v>4300</v>
+        <v>2200</v>
       </c>
       <c r="J40" s="6">
-        <v>4300</v>
+        <v>2200</v>
       </c>
       <c r="K40" s="6" t="s">
-        <v>612</v>
+        <v>370</v>
       </c>
       <c r="L40" s="6">
-        <v>65000</v>
+        <v>47000</v>
       </c>
       <c r="M40" s="6" t="s">
-        <v>231</v>
+        <v>360</v>
       </c>
       <c r="N40" s="6">
-        <v>52000</v>
+        <v>40000</v>
       </c>
       <c r="O40" s="6" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="P40" s="6">
-        <v>55000</v>
+        <v>38000</v>
       </c>
       <c r="Q40" s="6" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="R40" s="6" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="S40" s="6" t="s">
         <v>37</v>
@@ -13823,16 +13872,16 @@
         <v>37</v>
       </c>
       <c r="U40" s="6" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="V40" s="6" t="s">
         <v>150</v>
       </c>
       <c r="W40" s="6" t="s">
-        <v>588</v>
+        <v>353</v>
       </c>
       <c r="X40" s="6" t="s">
-        <v>588</v>
+        <v>109</v>
       </c>
       <c r="Y40" s="6" t="s">
         <v>579</v>
@@ -13846,58 +13895,58 @@
     </row>
     <row r="41" spans="1:27">
       <c r="A41" s="6">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B41" s="6" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="C41" s="6" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
       <c r="E41" s="13">
-        <v>43365.7868287037</v>
+        <v>43392.7518402778</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="G41" s="6">
-        <v>1133000</v>
+        <v>1869000</v>
       </c>
       <c r="H41" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I41" s="6">
-        <v>3800</v>
+        <v>4300</v>
       </c>
       <c r="J41" s="6">
-        <v>3800</v>
+        <v>4300</v>
       </c>
       <c r="K41" s="6" t="s">
-        <v>371</v>
+        <v>612</v>
       </c>
       <c r="L41" s="6">
-        <v>48000</v>
+        <v>65000</v>
       </c>
       <c r="M41" s="6" t="s">
-        <v>129</v>
+        <v>231</v>
       </c>
       <c r="N41" s="6">
-        <v>44000</v>
+        <v>52000</v>
       </c>
       <c r="O41" s="6" t="s">
-        <v>129</v>
+        <v>613</v>
       </c>
       <c r="P41" s="6">
-        <v>44000</v>
+        <v>55000</v>
       </c>
       <c r="Q41" s="6" t="s">
-        <v>621</v>
+        <v>614</v>
       </c>
       <c r="R41" s="6" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="S41" s="6" t="s">
         <v>37</v>
@@ -13906,16 +13955,16 @@
         <v>37</v>
       </c>
       <c r="U41" s="6" t="s">
-        <v>623</v>
+        <v>616</v>
       </c>
       <c r="V41" s="6" t="s">
-        <v>122</v>
+        <v>150</v>
       </c>
       <c r="W41" s="6" t="s">
-        <v>353</v>
+        <v>588</v>
       </c>
       <c r="X41" s="6" t="s">
-        <v>353</v>
+        <v>588</v>
       </c>
       <c r="Y41" s="6" t="s">
         <v>579</v>
@@ -13929,58 +13978,58 @@
     </row>
     <row r="42" spans="1:27">
       <c r="A42" s="6">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B42" s="6" t="s">
-        <v>624</v>
+        <v>617</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>625</v>
+        <v>618</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="E42" s="13">
-        <v>43332.8133796296</v>
+        <v>43365.7868287037</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>627</v>
+        <v>620</v>
       </c>
       <c r="G42" s="6">
-        <v>1875000</v>
+        <v>1133000</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I42" s="6">
-        <v>6400</v>
+        <v>3800</v>
       </c>
       <c r="J42" s="6">
-        <v>6400</v>
+        <v>3800</v>
       </c>
       <c r="K42" s="6" t="s">
-        <v>53</v>
+        <v>371</v>
       </c>
       <c r="L42" s="6">
-        <v>71000</v>
+        <v>48000</v>
       </c>
       <c r="M42" s="6" t="s">
-        <v>168</v>
+        <v>129</v>
       </c>
       <c r="N42" s="6">
-        <v>62000</v>
+        <v>44000</v>
       </c>
       <c r="O42" s="6" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="P42" s="6">
-        <v>60000</v>
+        <v>44000</v>
       </c>
       <c r="Q42" s="6" t="s">
-        <v>628</v>
+        <v>621</v>
       </c>
       <c r="R42" s="6" t="s">
-        <v>629</v>
+        <v>622</v>
       </c>
       <c r="S42" s="6" t="s">
         <v>37</v>
@@ -13989,16 +14038,16 @@
         <v>37</v>
       </c>
       <c r="U42" s="6" t="s">
-        <v>630</v>
+        <v>623</v>
       </c>
       <c r="V42" s="6" t="s">
-        <v>631</v>
+        <v>122</v>
       </c>
       <c r="W42" s="6" t="s">
-        <v>632</v>
+        <v>353</v>
       </c>
       <c r="X42" s="6" t="s">
-        <v>633</v>
+        <v>353</v>
       </c>
       <c r="Y42" s="6" t="s">
         <v>579</v>
@@ -14012,58 +14061,58 @@
     </row>
     <row r="43" spans="1:27">
       <c r="A43" s="6">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>634</v>
+        <v>624</v>
       </c>
       <c r="C43" s="6" t="s">
-        <v>635</v>
+        <v>625</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>636</v>
+        <v>626</v>
       </c>
       <c r="E43" s="13">
-        <v>43309.7505092593</v>
+        <v>43332.8133796296</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>637</v>
+        <v>627</v>
       </c>
       <c r="G43" s="6">
-        <v>1475000</v>
+        <v>1875000</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I43" s="6">
-        <v>7000</v>
+        <v>6400</v>
       </c>
       <c r="J43" s="6">
-        <v>7000</v>
+        <v>6400</v>
       </c>
       <c r="K43" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="L43" s="6">
+        <v>71000</v>
+      </c>
+      <c r="M43" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="N43" s="6">
+        <v>62000</v>
+      </c>
+      <c r="O43" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="L43" s="6">
+      <c r="P43" s="6">
         <v>60000</v>
       </c>
-      <c r="M43" s="6" t="s">
-        <v>612</v>
-      </c>
-      <c r="N43" s="6">
-        <v>65000</v>
-      </c>
-      <c r="O43" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="P43" s="6">
-        <v>62000</v>
-      </c>
       <c r="Q43" s="6" t="s">
-        <v>638</v>
+        <v>628</v>
       </c>
       <c r="R43" s="6" t="s">
-        <v>639</v>
+        <v>629</v>
       </c>
       <c r="S43" s="6" t="s">
         <v>37</v>
@@ -14072,22 +14121,22 @@
         <v>37</v>
       </c>
       <c r="U43" s="6" t="s">
-        <v>640</v>
+        <v>630</v>
       </c>
       <c r="V43" s="6" t="s">
-        <v>122</v>
+        <v>631</v>
       </c>
       <c r="W43" s="6" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="X43" s="6" t="s">
-        <v>388</v>
+        <v>633</v>
       </c>
       <c r="Y43" s="6" t="s">
         <v>579</v>
       </c>
       <c r="Z43" s="6" t="s">
-        <v>642</v>
+        <v>599</v>
       </c>
       <c r="AA43" s="6" t="s">
         <v>438</v>
@@ -14095,58 +14144,58 @@
     </row>
     <row r="44" spans="1:27">
       <c r="A44" s="6">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="C44" s="6" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="E44" s="13">
-        <v>43287.7170717593</v>
+        <v>43309.7505092593</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="G44" s="6">
-        <v>1419000</v>
+        <v>1475000</v>
       </c>
       <c r="H44" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I44" s="6">
-        <v>5900</v>
+        <v>7000</v>
       </c>
       <c r="J44" s="6">
-        <v>5900</v>
+        <v>7000</v>
       </c>
       <c r="K44" s="6" t="s">
-        <v>231</v>
+        <v>118</v>
       </c>
       <c r="L44" s="6">
-        <v>52000</v>
+        <v>60000</v>
       </c>
       <c r="M44" s="6" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="N44" s="6">
-        <v>55000</v>
+        <v>65000</v>
       </c>
       <c r="O44" s="6" t="s">
-        <v>279</v>
+        <v>168</v>
       </c>
       <c r="P44" s="6">
-        <v>57000</v>
+        <v>62000</v>
       </c>
       <c r="Q44" s="6" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
       <c r="R44" s="6" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="S44" s="6" t="s">
         <v>37</v>
@@ -14155,22 +14204,22 @@
         <v>37</v>
       </c>
       <c r="U44" s="6" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="V44" s="6" t="s">
-        <v>411</v>
+        <v>122</v>
       </c>
       <c r="W44" s="6" t="s">
-        <v>632</v>
+        <v>641</v>
       </c>
       <c r="X44" s="6" t="s">
-        <v>462</v>
+        <v>388</v>
       </c>
       <c r="Y44" s="6" t="s">
         <v>579</v>
       </c>
       <c r="Z44" s="6" t="s">
-        <v>124</v>
+        <v>642</v>
       </c>
       <c r="AA44" s="6" t="s">
         <v>438</v>
@@ -14178,58 +14227,58 @@
     </row>
     <row r="45" spans="1:27">
       <c r="A45" s="6">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>650</v>
+        <v>643</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>651</v>
+        <v>644</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>652</v>
+        <v>645</v>
       </c>
       <c r="E45" s="13">
-        <v>43273.7968287037</v>
+        <v>43287.7170717593</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>653</v>
+        <v>646</v>
       </c>
       <c r="G45" s="6">
-        <v>1887000</v>
+        <v>1419000</v>
       </c>
       <c r="H45" s="6" t="s">
         <v>49</v>
       </c>
       <c r="I45" s="6">
-        <v>8400</v>
+        <v>5900</v>
       </c>
       <c r="J45" s="6">
-        <v>8400</v>
+        <v>5900</v>
       </c>
       <c r="K45" s="6" t="s">
-        <v>531</v>
+        <v>231</v>
       </c>
       <c r="L45" s="6">
-        <v>72000</v>
+        <v>52000</v>
       </c>
       <c r="M45" s="6" t="s">
-        <v>654</v>
+        <v>613</v>
       </c>
       <c r="N45" s="6">
-        <v>77000</v>
+        <v>55000</v>
       </c>
       <c r="O45" s="6" t="s">
-        <v>433</v>
+        <v>279</v>
       </c>
       <c r="P45" s="6">
-        <v>81000</v>
+        <v>57000</v>
       </c>
       <c r="Q45" s="6" t="s">
-        <v>655</v>
+        <v>647</v>
       </c>
       <c r="R45" s="6" t="s">
-        <v>37</v>
+        <v>648</v>
       </c>
       <c r="S45" s="6" t="s">
         <v>37</v>
@@ -14238,16 +14287,16 @@
         <v>37</v>
       </c>
       <c r="U45" s="6" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="V45" s="6" t="s">
-        <v>162</v>
+        <v>411</v>
       </c>
       <c r="W45" s="6" t="s">
-        <v>388</v>
+        <v>632</v>
       </c>
       <c r="X45" s="6" t="s">
-        <v>109</v>
+        <v>462</v>
       </c>
       <c r="Y45" s="6" t="s">
         <v>579</v>
@@ -14256,6 +14305,89 @@
         <v>124</v>
       </c>
       <c r="AA45" s="6" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="46" spans="1:27">
+      <c r="A46" s="6">
+        <v>54</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>650</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>651</v>
+      </c>
+      <c r="D46" s="6" t="s">
+        <v>652</v>
+      </c>
+      <c r="E46" s="13">
+        <v>43273.7968287037</v>
+      </c>
+      <c r="F46" s="6" t="s">
+        <v>653</v>
+      </c>
+      <c r="G46" s="6">
+        <v>1887000</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="I46" s="6">
+        <v>8400</v>
+      </c>
+      <c r="J46" s="6">
+        <v>8400</v>
+      </c>
+      <c r="K46" s="6" t="s">
+        <v>531</v>
+      </c>
+      <c r="L46" s="6">
+        <v>72000</v>
+      </c>
+      <c r="M46" s="6" t="s">
+        <v>654</v>
+      </c>
+      <c r="N46" s="6">
+        <v>77000</v>
+      </c>
+      <c r="O46" s="6" t="s">
+        <v>433</v>
+      </c>
+      <c r="P46" s="6">
+        <v>81000</v>
+      </c>
+      <c r="Q46" s="6" t="s">
+        <v>655</v>
+      </c>
+      <c r="R46" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="S46" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="T46" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="U46" s="6" t="s">
+        <v>656</v>
+      </c>
+      <c r="V46" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="W46" s="6" t="s">
+        <v>388</v>
+      </c>
+      <c r="X46" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="Y46" s="6" t="s">
+        <v>579</v>
+      </c>
+      <c r="Z46" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="AA46" s="6" t="s">
         <v>438</v>
       </c>
     </row>
@@ -14269,23 +14401,23 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:AH45"/>
-  <sheetFormatPr defaultColWidth="9.81818181818182" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9.8141592920354" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="9.81818181818182" style="1" hidden="1" customWidth="1"/>
-    <col min="2" max="3" width="22.2727272727273" style="1" customWidth="1"/>
-    <col min="4" max="4" width="9.81818181818182" style="1"/>
-    <col min="5" max="5" width="11.8181818181818" style="2"/>
-    <col min="6" max="6" width="9.81818181818182" style="1"/>
-    <col min="8" max="9" width="9.81818181818182" style="1"/>
-    <col min="11" max="11" width="9.81818181818182" style="1"/>
-    <col min="13" max="13" width="9.81818181818182" style="1"/>
-    <col min="15" max="15" width="9.81818181818182" style="1"/>
-    <col min="17" max="32" width="9.81818181818182" style="1"/>
-    <col min="33" max="34" width="9.81818181818182" style="3"/>
-    <col min="35" max="16384" width="9.81818181818182" style="1"/>
+    <col min="1" max="1" width="9.8141592920354" style="1" hidden="1" customWidth="1"/>
+    <col min="2" max="3" width="22.2743362831858" style="1" customWidth="1"/>
+    <col min="4" max="4" width="9.8141592920354" style="1"/>
+    <col min="5" max="5" width="11.8141592920354" style="2"/>
+    <col min="6" max="6" width="9.8141592920354" style="1"/>
+    <col min="8" max="9" width="9.8141592920354" style="1"/>
+    <col min="11" max="11" width="9.8141592920354" style="1"/>
+    <col min="13" max="13" width="9.8141592920354" style="1"/>
+    <col min="15" max="15" width="9.8141592920354" style="1"/>
+    <col min="17" max="32" width="9.8141592920354" style="1"/>
+    <col min="33" max="34" width="9.8141592920354" style="3"/>
+    <col min="35" max="16384" width="9.8141592920354" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="14.75" spans="1:34">
+    <row r="1" ht="14.6" spans="1:34">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -14368,28 +14500,28 @@
         <v>26</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="AD1" s="5" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="AE1" s="5" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
     </row>
-    <row r="2" ht="14.75" spans="1:34">
+    <row r="2" ht="14.6" spans="1:34">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -14472,28 +14604,28 @@
         <v>64</v>
       </c>
       <c r="AB2" s="1" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="AC2" s="1" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="AD2" s="7" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="AE2" s="7" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="AF2" s="1" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="AG2" s="3" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="AH2" s="3" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
     </row>
-    <row r="3" ht="17.75" spans="1:34">
+    <row r="3" ht="16.5" spans="1:34">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -14561,7 +14693,7 @@
         <v>77</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="X3" s="1" t="s">
         <v>79</v>
@@ -14576,28 +14708,28 @@
         <v>79</v>
       </c>
       <c r="AB3" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="AC3" s="8" t="s">
+        <v>678</v>
+      </c>
+      <c r="AD3" s="7" t="s">
+        <v>679</v>
+      </c>
+      <c r="AE3" s="7" t="s">
+        <v>680</v>
+      </c>
+      <c r="AF3" s="1" t="s">
         <v>673</v>
       </c>
-      <c r="AC3" s="8" t="s">
-        <v>674</v>
-      </c>
-      <c r="AD3" s="7" t="s">
-        <v>675</v>
-      </c>
-      <c r="AE3" s="7" t="s">
-        <v>676</v>
-      </c>
-      <c r="AF3" s="1" t="s">
-        <v>669</v>
-      </c>
       <c r="AG3" s="3" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="AH3" s="3" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
     </row>
-    <row r="4" ht="17.75" spans="1:34">
+    <row r="4" ht="16.5" spans="1:34">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -14671,31 +14803,31 @@
         <v>95</v>
       </c>
       <c r="AA4" s="1" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="AB4" s="1" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="AC4" s="8" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="AD4" s="7" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="AE4" s="7" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="AF4" s="1" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="AG4" s="3" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="AH4" s="3" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
     </row>
-    <row r="5" ht="17.75" spans="1:34">
+    <row r="5" ht="16.5" spans="1:34">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -14772,28 +14904,28 @@
         <v>60</v>
       </c>
       <c r="AB5" s="1" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="AC5" s="8" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="AD5" s="7" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="AE5" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="AF5" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="AG5" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="AH5" s="3" t="s">
         <v>689</v>
       </c>
-      <c r="AF5" s="1" t="s">
-        <v>690</v>
-      </c>
-      <c r="AG5" s="3" t="s">
-        <v>691</v>
-      </c>
-      <c r="AH5" s="3" t="s">
-        <v>685</v>
-      </c>
     </row>
-    <row r="6" ht="17.75" spans="1:34">
+    <row r="6" ht="16.5" spans="1:34">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -14873,28 +15005,28 @@
         <v>60</v>
       </c>
       <c r="AB6" s="1" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="AC6" s="8" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="AD6" s="7" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="AE6" s="7" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="AF6" s="1" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="AG6" s="3" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="AH6" s="3" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
     </row>
-    <row r="7" ht="17.75" spans="1:34">
+    <row r="7" ht="16.5" spans="1:34">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -14974,28 +15106,28 @@
         <v>60</v>
       </c>
       <c r="AB7" s="1" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="AC7" s="8" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="AD7" s="7" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="AE7" s="7" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="AF7" s="1" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="AG7" s="3" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="AH7" s="3" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
     </row>
-    <row r="8" ht="17.75" spans="1:34">
+    <row r="8" ht="16.5" spans="1:34">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -15078,28 +15210,28 @@
         <v>60</v>
       </c>
       <c r="AB8" s="1" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="AC8" s="8" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="AD8" s="7" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="AE8" s="7" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="AF8" s="1" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="AG8" s="3" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="AH8" s="3" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
     </row>
-    <row r="9" ht="17.75" spans="1:34">
+    <row r="9" ht="16.5" spans="1:34">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -15182,28 +15314,28 @@
         <v>60</v>
       </c>
       <c r="AB9" s="1" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="AC9" s="8" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="AD9" s="7" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="AE9" s="7" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="AF9" s="7" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="AG9" s="3" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="AH9" s="3" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
     </row>
-    <row r="10" ht="17.75" spans="1:34">
+    <row r="10" ht="16.5" spans="1:34">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -15283,28 +15415,28 @@
         <v>60</v>
       </c>
       <c r="AB10" s="1" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="AC10" s="8" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="AD10" s="7" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="AE10" s="7" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="AF10" s="1" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="AG10" s="3" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="AH10" s="3" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
     </row>
-    <row r="11" ht="14.75" spans="1:34">
+    <row r="11" ht="14.6" spans="1:34">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -15384,28 +15516,28 @@
         <v>60</v>
       </c>
       <c r="AB11" s="1" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="AC11" s="1" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="AD11" s="7" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="AE11" s="7" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="AF11" s="1" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="AG11" s="3" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="AH11" s="3" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
     </row>
-    <row r="12" ht="17.75" spans="1:34">
+    <row r="12" ht="16.5" spans="1:34">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -15482,28 +15614,28 @@
         <v>60</v>
       </c>
       <c r="AB12" s="1" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="AC12" s="8" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="AD12" s="7" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="AE12" s="7" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="AF12" s="1" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="AG12" s="3" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="AH12" s="3" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
     </row>
-    <row r="13" ht="17.75" spans="1:34">
+    <row r="13" ht="16.5" spans="1:34">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -15580,28 +15712,28 @@
         <v>60</v>
       </c>
       <c r="AB13" s="1" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="AC13" s="8" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="AD13" s="7" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="AE13" s="7" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="AF13" s="1" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="AG13" s="3" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="AH13" s="3" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
     </row>
-    <row r="14" ht="17.75" spans="1:34">
+    <row r="14" ht="16.5" spans="1:34">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -15681,28 +15813,28 @@
         <v>60</v>
       </c>
       <c r="AB14" s="1" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="AC14" s="8" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="AD14" s="7" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="AE14" s="7" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="AF14" s="1" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="AG14" s="3" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="AH14" s="3" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
     </row>
-    <row r="15" ht="17.75" spans="1:34">
+    <row r="15" ht="16.5" spans="1:34">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -15782,28 +15914,28 @@
         <v>60</v>
       </c>
       <c r="AB15" s="1" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="AC15" s="8" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="AD15" s="7" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="AE15" s="7" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="AF15" s="1" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="AG15" s="3" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="AH15" s="3" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
     </row>
-    <row r="16" ht="14.75" spans="1:34">
+    <row r="16" ht="14.6" spans="1:34">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -15874,7 +16006,7 @@
         <v>285</v>
       </c>
       <c r="Y16" s="1" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="Z16" s="1" t="s">
         <v>287</v>
@@ -15883,28 +16015,28 @@
         <v>60</v>
       </c>
       <c r="AB16" s="1" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="AC16" s="1" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="AD16" s="7" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="AE16" s="7" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="AF16" s="1" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="AG16" s="3" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="AH16" s="3" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
     </row>
-    <row r="17" ht="14.75" spans="1:34">
+    <row r="17" ht="14.6" spans="1:34">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -15987,28 +16119,28 @@
         <v>60</v>
       </c>
       <c r="AB17" s="1" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="AC17" s="1" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="AD17" s="7" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="AE17" s="7" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="AF17" s="1" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="AG17" s="3" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="AH17" s="3" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
     </row>
-    <row r="18" ht="17.75" spans="1:34">
+    <row r="18" ht="16.5" spans="1:34">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -16064,7 +16196,7 @@
         <v>309</v>
       </c>
       <c r="T18" s="1" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
       <c r="U18" s="6" t="s">
         <v>311</v>
@@ -16082,34 +16214,34 @@
         <v>286</v>
       </c>
       <c r="Z18" s="1" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="AA18" s="1" t="s">
         <v>60</v>
       </c>
       <c r="AB18" s="1" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="AC18" s="8" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="AD18" s="7" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="AE18" s="7" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="AF18" s="1" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="AG18" s="3" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="AH18" s="3" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
     </row>
-    <row r="19" ht="17.75" spans="1:34">
+    <row r="19" ht="16.5" spans="1:34">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -16183,31 +16315,31 @@
         <v>324</v>
       </c>
       <c r="AA19" s="1" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="AB19" s="1" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
       <c r="AC19" s="8" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="AD19" s="7" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="AE19" s="7" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
       <c r="AF19" s="1" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="AG19" s="3" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="AH19" s="3" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
     </row>
-    <row r="20" ht="17.75" spans="1:34">
+    <row r="20" ht="16.5" spans="1:34">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -16284,31 +16416,31 @@
         <v>80</v>
       </c>
       <c r="AA20" s="1" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="AB20" s="1" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="AC20" s="8" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
       <c r="AD20" s="7" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="AE20" s="7" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="AF20" s="1" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="AG20" s="3" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
       <c r="AH20" s="3" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
     </row>
-    <row r="21" ht="17.75" spans="1:34">
+    <row r="21" ht="16.5" spans="1:34">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -16385,28 +16517,28 @@
         <v>355</v>
       </c>
       <c r="AB21" s="1" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
       <c r="AC21" s="8" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="AD21" s="7" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="AE21" s="7" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="AF21" s="1" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="AG21" s="3" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="AH21" s="3" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
     </row>
-    <row r="22" ht="14.75" spans="1:34">
+    <row r="22" ht="14.6" spans="1:34">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -16483,28 +16615,28 @@
         <v>355</v>
       </c>
       <c r="AB22" s="1" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
       <c r="AC22" s="1" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="AD22" s="7" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
       <c r="AE22" s="7" t="s">
+        <v>801</v>
+      </c>
+      <c r="AF22" s="1" t="s">
+        <v>748</v>
+      </c>
+      <c r="AG22" s="3" t="s">
+        <v>802</v>
+      </c>
+      <c r="AH22" s="3" t="s">
         <v>797</v>
       </c>
-      <c r="AF22" s="1" t="s">
-        <v>744</v>
-      </c>
-      <c r="AG22" s="3" t="s">
-        <v>798</v>
-      </c>
-      <c r="AH22" s="3" t="s">
-        <v>793</v>
-      </c>
     </row>
-    <row r="23" ht="17.75" spans="1:34">
+    <row r="23" ht="16.5" spans="1:34">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -16581,31 +16713,31 @@
         <v>80</v>
       </c>
       <c r="AA23" s="1" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="AB23" s="1" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
       <c r="AC23" s="8" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="AD23" s="7" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
       <c r="AE23" s="7" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="AF23" s="1" t="s">
-        <v>804</v>
+        <v>808</v>
       </c>
       <c r="AG23" s="3" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="AH23" s="3" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
     </row>
-    <row r="24" ht="14.75" spans="1:34">
+    <row r="24" ht="14.6" spans="1:34">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -16688,28 +16820,28 @@
         <v>413</v>
       </c>
       <c r="AB24" s="1" t="s">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="AC24" s="9" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="AD24" s="7" t="s">
-        <v>808</v>
+        <v>812</v>
       </c>
       <c r="AE24" s="7" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
       <c r="AF24" s="1" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="AG24" s="3" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="AH24" s="3" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
     </row>
-    <row r="25" ht="17.75" spans="1:34">
+    <row r="25" ht="16.5" spans="1:34">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -16764,8 +16896,8 @@
       <c r="R25" s="1" t="s">
         <v>421</v>
       </c>
-      <c r="S25" s="10"/>
-      <c r="T25" s="10" t="s">
+      <c r="S25" s="3"/>
+      <c r="T25" s="3" t="s">
         <v>422</v>
       </c>
       <c r="U25" s="6" t="s">
@@ -16790,28 +16922,28 @@
         <v>413</v>
       </c>
       <c r="AB25" s="1" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="AC25" s="8" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="AD25" s="7" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="AE25" s="7" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="AF25" s="1" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="AG25" s="3" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="AH25" s="3" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
     </row>
-    <row r="26" ht="17.75" spans="1:34">
+    <row r="26" ht="16.5" spans="1:34">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -16866,8 +16998,8 @@
       <c r="R26" s="1" t="s">
         <v>436</v>
       </c>
-      <c r="S26" s="10"/>
-      <c r="T26" s="10"/>
+      <c r="S26" s="3"/>
+      <c r="T26" s="3"/>
       <c r="U26" s="6" t="s">
         <v>437</v>
       </c>
@@ -16887,31 +17019,31 @@
         <v>354</v>
       </c>
       <c r="AA26" s="1" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="AB26" s="1" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="AC26" s="8" t="s">
+        <v>825</v>
+      </c>
+      <c r="AD26" s="7" t="s">
+        <v>826</v>
+      </c>
+      <c r="AE26" s="7" t="s">
+        <v>827</v>
+      </c>
+      <c r="AF26" s="7" t="s">
+        <v>827</v>
+      </c>
+      <c r="AG26" s="3" t="s">
         <v>821</v>
       </c>
-      <c r="AD26" s="7" t="s">
+      <c r="AH26" s="3" t="s">
         <v>822</v>
       </c>
-      <c r="AE26" s="7" t="s">
-        <v>823</v>
-      </c>
-      <c r="AF26" s="7" t="s">
-        <v>823</v>
-      </c>
-      <c r="AG26" s="3" t="s">
-        <v>817</v>
-      </c>
-      <c r="AH26" s="3" t="s">
-        <v>818</v>
-      </c>
     </row>
-    <row r="27" ht="14.75" spans="1:34">
+    <row r="27" ht="14.6" spans="1:34">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -16966,8 +17098,8 @@
       <c r="R27" s="1" t="s">
         <v>448</v>
       </c>
-      <c r="S27" s="10"/>
-      <c r="T27" s="10" t="s">
+      <c r="S27" s="3"/>
+      <c r="T27" s="3" t="s">
         <v>282</v>
       </c>
       <c r="U27" s="6" t="s">
@@ -16989,31 +17121,31 @@
         <v>80</v>
       </c>
       <c r="AA27" s="1" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="AB27" s="1" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="AC27" s="9" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="AD27" s="7" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="AE27" s="7" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="AF27" s="1" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="AG27" s="3" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="AH27" s="3" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
     </row>
-    <row r="28" ht="14.75" spans="1:34">
+    <row r="28" ht="14.6" spans="1:34">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -17068,12 +17200,12 @@
       <c r="R28" s="1" t="s">
         <v>459</v>
       </c>
-      <c r="S28" s="10"/>
-      <c r="T28" s="10" t="s">
+      <c r="S28" s="3"/>
+      <c r="T28" s="3" t="s">
         <v>460</v>
       </c>
       <c r="U28" s="6" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="V28" s="1" t="s">
         <v>150</v>
@@ -17091,31 +17223,31 @@
         <v>80</v>
       </c>
       <c r="AA28" s="1" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="AB28" s="1" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="AC28" s="1" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="AD28" s="7" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="AE28" s="7" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="AF28" s="1" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="AG28" s="3" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="AH28" s="3" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
     </row>
-    <row r="29" ht="14.75" spans="1:34">
+    <row r="29" ht="14.6" spans="1:34">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -17170,8 +17302,8 @@
       <c r="R29" s="1" t="s">
         <v>486</v>
       </c>
-      <c r="S29" s="10"/>
-      <c r="T29" s="10" t="s">
+      <c r="S29" s="3"/>
+      <c r="T29" s="3" t="s">
         <v>487</v>
       </c>
       <c r="U29" s="6" t="s">
@@ -17193,31 +17325,31 @@
         <v>490</v>
       </c>
       <c r="AA29" s="1" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="AB29" s="1" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="AC29" s="1" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
       <c r="AD29" s="7" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="AE29" s="7" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="AF29" s="7" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="AG29" s="3" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="AH29" s="3" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
     </row>
-    <row r="30" ht="14.75" spans="1:34">
+    <row r="30" ht="14.6" spans="1:34">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -17272,8 +17404,8 @@
       <c r="R30" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="S30" s="10"/>
-      <c r="T30" s="10" t="s">
+      <c r="S30" s="3"/>
+      <c r="T30" s="3" t="s">
         <v>505</v>
       </c>
       <c r="U30" s="6" t="s">
@@ -17295,31 +17427,31 @@
         <v>324</v>
       </c>
       <c r="AA30" s="1" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="AB30" s="1" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="AC30" s="1" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="AD30" s="7" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
       <c r="AE30" s="7" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="AF30" s="1" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="AG30" s="3" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
       <c r="AH30" s="3" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
     </row>
-    <row r="31" ht="14.75" spans="1:34">
+    <row r="31" ht="14.6" spans="1:34">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -17374,8 +17506,8 @@
       <c r="R31" s="1" t="s">
         <v>523</v>
       </c>
-      <c r="S31" s="10"/>
-      <c r="T31" s="10"/>
+      <c r="S31" s="3"/>
+      <c r="T31" s="3"/>
       <c r="U31" s="6" t="s">
         <v>524</v>
       </c>
@@ -17386,7 +17518,7 @@
         <v>438</v>
       </c>
       <c r="X31" s="1" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="Y31" s="1" t="s">
         <v>42</v>
@@ -17395,31 +17527,31 @@
         <v>80</v>
       </c>
       <c r="AA31" s="1" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="AB31" s="1" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
       <c r="AC31" s="1" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="AD31" s="7" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
       <c r="AE31" s="7" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="AF31" s="1" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
       <c r="AG31" s="3" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="AH31" s="3" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
     </row>
-    <row r="32" ht="17.75" spans="1:34">
+    <row r="32" ht="16.5" spans="1:34">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -17474,8 +17606,8 @@
       <c r="R32" s="1" t="s">
         <v>533</v>
       </c>
-      <c r="S32" s="10"/>
-      <c r="T32" s="10" t="s">
+      <c r="S32" s="3"/>
+      <c r="T32" s="3" t="s">
         <v>199</v>
       </c>
       <c r="U32" s="6" t="s">
@@ -17485,7 +17617,7 @@
         <v>92</v>
       </c>
       <c r="W32" s="1" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
       <c r="X32" s="1" t="s">
         <v>479</v>
@@ -17497,31 +17629,31 @@
         <v>536</v>
       </c>
       <c r="AA32" s="1" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="AB32" s="1" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="AC32" s="8" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="AD32" s="7" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="AE32" s="7" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="AF32" s="1" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="AG32" s="3" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="AH32" s="3" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
     </row>
-    <row r="33" ht="14.75" spans="1:34">
+    <row r="33" ht="14.6" spans="1:34">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -17576,8 +17708,8 @@
       <c r="R33" s="1" t="s">
         <v>546</v>
       </c>
-      <c r="S33" s="10"/>
-      <c r="T33" s="10"/>
+      <c r="S33" s="3"/>
+      <c r="T33" s="3"/>
       <c r="U33" s="6" t="s">
         <v>547</v>
       </c>
@@ -17600,28 +17732,28 @@
         <v>548</v>
       </c>
       <c r="AB33" s="1" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="AC33" s="1" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="AD33" s="7" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="AE33" s="7" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="AF33" s="1" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="AG33" s="3" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="AH33" s="3" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
     </row>
-    <row r="34" ht="14.75" spans="1:34">
+    <row r="34" ht="14.6" spans="1:34">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -17676,8 +17808,8 @@
       <c r="R34" s="1" t="s">
         <v>555</v>
       </c>
-      <c r="S34" s="10"/>
-      <c r="T34" s="10" t="s">
+      <c r="S34" s="3"/>
+      <c r="T34" s="3" t="s">
         <v>556</v>
       </c>
       <c r="U34" s="6" t="s">
@@ -17702,28 +17834,28 @@
         <v>548</v>
       </c>
       <c r="AB34" s="1" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="AC34" s="1" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
       <c r="AD34" s="7" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="AE34" s="7" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="AF34" s="1" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
       <c r="AG34" s="3" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="AH34" s="3" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
     </row>
-    <row r="35" ht="17.75" spans="1:34">
+    <row r="35" ht="16.5" spans="1:34">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -17788,7 +17920,7 @@
         <v>249</v>
       </c>
       <c r="W35" s="1" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
       <c r="X35" s="1" t="s">
         <v>479</v>
@@ -17803,28 +17935,28 @@
         <v>548</v>
       </c>
       <c r="AB35" s="1" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="AC35" s="8" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
       <c r="AD35" s="7" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
       <c r="AE35" s="7" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
       <c r="AF35" s="7" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
       <c r="AG35" s="3" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
       <c r="AH35" s="3" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
     </row>
-    <row r="36" ht="17.75" spans="1:34">
+    <row r="36" ht="16.5" spans="1:34">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -17901,28 +18033,28 @@
         <v>548</v>
       </c>
       <c r="AB36" s="1" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
       <c r="AC36" s="8" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
       <c r="AD36" s="7" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
       <c r="AE36" s="7" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
       <c r="AF36" s="1" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="AG36" s="3" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
       <c r="AH36" s="3" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
     </row>
-    <row r="37" ht="17.75" spans="1:34">
+    <row r="37" ht="16.5" spans="1:34">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -17999,28 +18131,28 @@
         <v>438</v>
       </c>
       <c r="AB37" s="1" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
       <c r="AC37" s="8" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="AD37" s="7" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
       <c r="AE37" s="7" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="AF37" s="1" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="AG37" s="3" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
       <c r="AH37" s="3" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
     </row>
-    <row r="38" ht="14.75" spans="1:34">
+    <row r="38" ht="14.6" spans="1:34">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -18097,28 +18229,28 @@
         <v>438</v>
       </c>
       <c r="AB38" s="1" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="AC38" s="1" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="AD38" s="7" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="AE38" s="7" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="AF38" s="1" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="AG38" s="3" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="AH38" s="3" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
     </row>
-    <row r="39" ht="17.75" spans="1:34">
+    <row r="39" ht="16.5" spans="1:34">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -18195,28 +18327,28 @@
         <v>438</v>
       </c>
       <c r="AB39" s="1" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="AC39" s="8" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="AD39" s="7" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="AE39" s="7" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="AF39" s="7" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="AG39" s="3" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="AH39" s="3" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
     </row>
-    <row r="40" ht="17.75" spans="1:34">
+    <row r="40" ht="16.5" spans="1:34">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -18293,28 +18425,28 @@
         <v>438</v>
       </c>
       <c r="AB40" s="1" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="AC40" s="8" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="AD40" s="7" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="AE40" s="7" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="AF40" s="7" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="AG40" s="3" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="AH40" s="3" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
     </row>
-    <row r="41" ht="17.75" spans="1:34">
+    <row r="41" ht="16.5" spans="1:34">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -18391,28 +18523,28 @@
         <v>438</v>
       </c>
       <c r="AB41" s="1" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="AC41" s="8" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="AD41" s="7" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="AE41" s="7" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="AF41" s="7" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="AG41" s="3" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="AH41" s="3" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
     </row>
-    <row r="42" ht="17.75" spans="1:34">
+    <row r="42" ht="16.5" spans="1:34">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -18489,28 +18621,28 @@
         <v>438</v>
       </c>
       <c r="AB42" s="1" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="AC42" s="8" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
       <c r="AD42" s="7" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="AE42" s="7" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="AF42" s="1" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="AG42" s="3" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="AH42" s="3" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
     </row>
-    <row r="43" ht="17.75" spans="1:34">
+    <row r="43" ht="16.5" spans="1:34">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -18587,28 +18719,28 @@
         <v>438</v>
       </c>
       <c r="AB43" s="1" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="AC43" s="8" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="AD43" s="7" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="AE43" s="7" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="AF43" s="7" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="AG43" s="3" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="AH43" s="3" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
     </row>
-    <row r="44" ht="17.75" spans="1:34">
+    <row r="44" ht="16.5" spans="1:34">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -18685,28 +18817,28 @@
         <v>438</v>
       </c>
       <c r="AB44" s="1" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="AC44" s="8" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="AD44" s="7" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="AE44" s="7" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="AF44" s="1" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="AG44" s="3" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="AH44" s="3" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
     </row>
-    <row r="45" ht="15.25" spans="1:34">
+    <row r="45" ht="15" spans="1:34">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -18758,8 +18890,8 @@
       <c r="Q45" s="1" t="s">
         <v>655</v>
       </c>
-      <c r="R45" s="11" t="s">
-        <v>933</v>
+      <c r="R45" s="10" t="s">
+        <v>937</v>
       </c>
       <c r="U45" s="6" t="s">
         <v>656</v>
@@ -18783,25 +18915,25 @@
         <v>438</v>
       </c>
       <c r="AB45" s="1" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="AC45" s="1" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="AD45" s="7" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="AE45" s="7" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="AF45" s="1" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="AG45" s="3" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="AH45" s="3" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
     </row>
   </sheetData>
